--- a/research/traditional_assets/database/data/bulgaria/bulgaria_building_materials.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_building_materials.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1053109386789026</v>
+        <v>0.1052461277402237</v>
       </c>
       <c r="C2">
-        <v>31.48604992735246</v>
+        <v>31.20092891353059</v>
       </c>
       <c r="D2">
-        <v>29.36604992735246</v>
+        <v>29.39446891353059</v>
       </c>
       <c r="E2">
-        <v>-0.654</v>
+        <v>-0.34046</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.31354</v>
       </c>
       <c r="G2">
         <v>2.12</v>
@@ -1451,28 +1451,28 @@
         <v>2.07</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.015771062</v>
       </c>
       <c r="N2">
-        <v>2.07</v>
+        <v>2.054228938000001</v>
       </c>
       <c r="O2">
-        <v>0.207</v>
+        <v>0.2054228938000001</v>
       </c>
       <c r="P2">
-        <v>1.863</v>
+        <v>1.8488060442</v>
       </c>
       <c r="Q2">
-        <v>2.493</v>
+        <v>2.478806044200001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1053109386789026</v>
+        <v>0.1058519472123472</v>
       </c>
       <c r="T2">
-        <v>0.920615294616134</v>
+        <v>0.9289845245671897</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>131.2530506823194</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1052461277402237</v>
+        <v>0.1051813168015448</v>
       </c>
       <c r="C3">
-        <v>31.20092891353059</v>
+        <v>30.9158629579223</v>
       </c>
       <c r="D3">
-        <v>29.39446891353059</v>
+        <v>29.4229429579223</v>
       </c>
       <c r="E3">
-        <v>-0.34046</v>
+        <v>-0.02692000000000005</v>
       </c>
       <c r="F3">
-        <v>0.31354</v>
+        <v>0.62708</v>
       </c>
       <c r="G3">
         <v>2.12</v>
@@ -1533,28 +1533,28 @@
         <v>2.07</v>
       </c>
       <c r="M3">
-        <v>0.015771062</v>
+        <v>0.031542124</v>
       </c>
       <c r="N3">
-        <v>2.054228938000001</v>
+        <v>2.038457876</v>
       </c>
       <c r="O3">
-        <v>0.2054228938000001</v>
+        <v>0.2038457876000001</v>
       </c>
       <c r="P3">
-        <v>1.8488060442</v>
+        <v>1.8346120884</v>
       </c>
       <c r="Q3">
-        <v>2.478806044200001</v>
+        <v>2.4646120884</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1058519472123472</v>
+        <v>0.1064039967362702</v>
       </c>
       <c r="T3">
-        <v>0.9289845245671897</v>
+        <v>0.9375245551294916</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>131.2530506823194</v>
+        <v>65.62652534115966</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1051813168015448</v>
+        <v>0.1051165058628659</v>
       </c>
       <c r="C4">
-        <v>30.9158629579223</v>
+        <v>30.63085222068532</v>
       </c>
       <c r="D4">
-        <v>29.4229429579223</v>
+        <v>29.45147222068532</v>
       </c>
       <c r="E4">
-        <v>-0.02692000000000005</v>
+        <v>0.2866199999999999</v>
       </c>
       <c r="F4">
-        <v>0.62708</v>
+        <v>0.9406199999999999</v>
       </c>
       <c r="G4">
         <v>2.12</v>
@@ -1615,28 +1615,28 @@
         <v>2.07</v>
       </c>
       <c r="M4">
-        <v>0.031542124</v>
+        <v>0.04731318599999999</v>
       </c>
       <c r="N4">
-        <v>2.038457876</v>
+        <v>2.022686814</v>
       </c>
       <c r="O4">
-        <v>0.2038457876000001</v>
+        <v>0.2022686814000001</v>
       </c>
       <c r="P4">
-        <v>1.8346120884</v>
+        <v>1.8204181326</v>
       </c>
       <c r="Q4">
-        <v>2.4646120884</v>
+        <v>2.4504181326</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1064039967362702</v>
+        <v>0.106967428724604</v>
       </c>
       <c r="T4">
-        <v>0.9375245551294916</v>
+        <v>0.9462406687961706</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>65.62652534115966</v>
+        <v>43.75101689410645</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1051165058628659</v>
+        <v>0.105051694924187</v>
       </c>
       <c r="C5">
-        <v>30.63085222068532</v>
+        <v>30.3458968625991</v>
       </c>
       <c r="D5">
-        <v>29.45147222068532</v>
+        <v>29.4800568625991</v>
       </c>
       <c r="E5">
-        <v>0.2866199999999999</v>
+        <v>0.6001599999999999</v>
       </c>
       <c r="F5">
-        <v>0.9406199999999999</v>
+        <v>1.25416</v>
       </c>
       <c r="G5">
         <v>2.12</v>
@@ -1697,28 +1697,28 @@
         <v>2.07</v>
       </c>
       <c r="M5">
-        <v>0.04731318599999999</v>
+        <v>0.063084248</v>
       </c>
       <c r="N5">
-        <v>2.022686814</v>
+        <v>2.006915752</v>
       </c>
       <c r="O5">
-        <v>0.2022686814000001</v>
+        <v>0.2006915752</v>
       </c>
       <c r="P5">
-        <v>1.8204181326</v>
+        <v>1.8062241768</v>
       </c>
       <c r="Q5">
-        <v>2.4504181326</v>
+        <v>2.4362241768</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.106967428724604</v>
+        <v>0.1075425988793615</v>
       </c>
       <c r="T5">
-        <v>0.9462406687961706</v>
+        <v>0.9551383681642391</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>43.75101689410645</v>
+        <v>32.81326267057983</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.105051694924187</v>
+        <v>0.1049868839855081</v>
       </c>
       <c r="C6">
-        <v>30.3458968625991</v>
+        <v>30.06099704506791</v>
       </c>
       <c r="D6">
-        <v>29.4800568625991</v>
+        <v>29.50869704506791</v>
       </c>
       <c r="E6">
-        <v>0.6001599999999999</v>
+        <v>0.9137000000000001</v>
       </c>
       <c r="F6">
-        <v>1.25416</v>
+        <v>1.5677</v>
       </c>
       <c r="G6">
         <v>2.12</v>
@@ -1779,28 +1779,28 @@
         <v>2.07</v>
       </c>
       <c r="M6">
-        <v>0.063084248</v>
+        <v>0.07885531</v>
       </c>
       <c r="N6">
-        <v>2.006915752</v>
+        <v>1.99114469</v>
       </c>
       <c r="O6">
-        <v>0.2006915752</v>
+        <v>0.199114469</v>
       </c>
       <c r="P6">
-        <v>1.8062241768</v>
+        <v>1.792030221</v>
       </c>
       <c r="Q6">
-        <v>2.4362241768</v>
+        <v>2.422030221</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1075425988793615</v>
+        <v>0.1081298778794822</v>
       </c>
       <c r="T6">
-        <v>0.9551383681642391</v>
+        <v>0.9642233875190035</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>32.81326267057983</v>
+        <v>26.25061013646387</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1049868839855081</v>
+        <v>0.1049220730468292</v>
       </c>
       <c r="C7">
-        <v>30.06099704506791</v>
+        <v>29.77615293012386</v>
       </c>
       <c r="D7">
-        <v>29.50869704506791</v>
+        <v>29.53739293012385</v>
       </c>
       <c r="E7">
-        <v>0.9137000000000001</v>
+        <v>1.22724</v>
       </c>
       <c r="F7">
-        <v>1.5677</v>
+        <v>1.88124</v>
       </c>
       <c r="G7">
         <v>2.12</v>
@@ -1861,28 +1861,28 @@
         <v>2.07</v>
       </c>
       <c r="M7">
-        <v>0.07885531</v>
+        <v>0.094626372</v>
       </c>
       <c r="N7">
-        <v>1.99114469</v>
+        <v>1.975373628</v>
       </c>
       <c r="O7">
-        <v>0.199114469</v>
+        <v>0.1975373628</v>
       </c>
       <c r="P7">
-        <v>1.792030221</v>
+        <v>1.7778362652</v>
       </c>
       <c r="Q7">
-        <v>2.422030221</v>
+        <v>2.4078362652</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1081298778794822</v>
+        <v>0.1087296521774778</v>
       </c>
       <c r="T7">
-        <v>0.9642233875190035</v>
+        <v>0.9735017051579119</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.25061013646387</v>
+        <v>21.87550844705322</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1049220730468292</v>
+        <v>0.1048572621081503</v>
       </c>
       <c r="C8">
-        <v>29.77615293012386</v>
+        <v>29.4913646804299</v>
       </c>
       <c r="D8">
-        <v>29.53739293012385</v>
+        <v>29.5661446804299</v>
       </c>
       <c r="E8">
-        <v>1.22724</v>
+        <v>1.54078</v>
       </c>
       <c r="F8">
-        <v>1.88124</v>
+        <v>2.19478</v>
       </c>
       <c r="G8">
         <v>2.12</v>
@@ -1943,28 +1943,28 @@
         <v>2.07</v>
       </c>
       <c r="M8">
-        <v>0.09462637199999999</v>
+        <v>0.110397434</v>
       </c>
       <c r="N8">
-        <v>1.975373628</v>
+        <v>1.959602566</v>
       </c>
       <c r="O8">
-        <v>0.1975373628</v>
+        <v>0.1959602566</v>
       </c>
       <c r="P8">
-        <v>1.7778362652</v>
+        <v>1.7636423094</v>
       </c>
       <c r="Q8">
-        <v>2.4078362652</v>
+        <v>2.3936423094</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1087296521774778</v>
+        <v>0.1093423248474734</v>
       </c>
       <c r="T8">
-        <v>0.9735017051579119</v>
+        <v>0.9829795565094849</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>21.87550844705322</v>
+        <v>18.75043581175991</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1048572621081503</v>
+        <v>0.1047924511694714</v>
       </c>
       <c r="C9">
-        <v>29.49136468042989</v>
+        <v>29.20663245928301</v>
       </c>
       <c r="D9">
-        <v>29.56614468042989</v>
+        <v>29.59495245928301</v>
       </c>
       <c r="E9">
-        <v>1.54078</v>
+        <v>1.85432</v>
       </c>
       <c r="F9">
-        <v>2.19478</v>
+        <v>2.50832</v>
       </c>
       <c r="G9">
         <v>2.12</v>
@@ -2025,28 +2025,28 @@
         <v>2.07</v>
       </c>
       <c r="M9">
-        <v>0.110397434</v>
+        <v>0.126168496</v>
       </c>
       <c r="N9">
-        <v>1.959602566</v>
+        <v>1.943831504</v>
       </c>
       <c r="O9">
-        <v>0.1959602566</v>
+        <v>0.1943831504</v>
       </c>
       <c r="P9">
-        <v>1.7636423094</v>
+        <v>1.7494483536</v>
       </c>
       <c r="Q9">
-        <v>2.3936423094</v>
+        <v>2.3794483536</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1093423248474734</v>
+        <v>0.1099683164885558</v>
       </c>
       <c r="T9">
-        <v>0.9829795565094851</v>
+        <v>0.9926634481078315</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.7504358117599</v>
+        <v>16.40663133528992</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1047924511694714</v>
+        <v>0.1047276402307925</v>
       </c>
       <c r="C10">
-        <v>29.20663245928301</v>
+        <v>28.92195643061722</v>
       </c>
       <c r="D10">
-        <v>29.59495245928301</v>
+        <v>29.62381643061722</v>
       </c>
       <c r="E10">
-        <v>1.85432</v>
+        <v>2.16786</v>
       </c>
       <c r="F10">
-        <v>2.50832</v>
+        <v>2.82186</v>
       </c>
       <c r="G10">
         <v>2.12</v>
@@ -2107,28 +2107,28 @@
         <v>2.07</v>
       </c>
       <c r="M10">
-        <v>0.126168496</v>
+        <v>0.141939558</v>
       </c>
       <c r="N10">
-        <v>1.943831504</v>
+        <v>1.928060442</v>
       </c>
       <c r="O10">
-        <v>0.1943831504</v>
+        <v>0.1928060442</v>
       </c>
       <c r="P10">
-        <v>1.7494483536</v>
+        <v>1.7352543978</v>
       </c>
       <c r="Q10">
-        <v>2.3794483536</v>
+        <v>2.3652543978</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1099683164885558</v>
+        <v>0.110608066187684</v>
       </c>
       <c r="T10">
-        <v>0.9926634481078315</v>
+        <v>1.002560172488559</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.40663133528992</v>
+        <v>14.58367229803548</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1047276402307925</v>
+        <v>0.1046628292921136</v>
       </c>
       <c r="C11">
-        <v>28.92195643061722</v>
+        <v>28.63733675900665</v>
       </c>
       <c r="D11">
-        <v>29.62381643061722</v>
+        <v>29.65273675900665</v>
       </c>
       <c r="E11">
-        <v>2.16786</v>
+        <v>2.4814</v>
       </c>
       <c r="F11">
-        <v>2.82186</v>
+        <v>3.1354</v>
       </c>
       <c r="G11">
         <v>2.12</v>
@@ -2189,28 +2189,28 @@
         <v>2.07</v>
       </c>
       <c r="M11">
-        <v>0.141939558</v>
+        <v>0.15771062</v>
       </c>
       <c r="N11">
-        <v>1.928060442</v>
+        <v>1.91228938</v>
       </c>
       <c r="O11">
-        <v>0.1928060442</v>
+        <v>0.191228938</v>
       </c>
       <c r="P11">
-        <v>1.7352543978</v>
+        <v>1.721060442</v>
       </c>
       <c r="Q11">
-        <v>2.3652543978</v>
+        <v>2.351060442</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.110608066187684</v>
+        <v>0.1112620325467929</v>
       </c>
       <c r="T11">
-        <v>1.002560172488559</v>
+        <v>1.012676824077748</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.58367229803548</v>
+        <v>13.12530506823193</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1046628292921136</v>
+        <v>0.1047465183534347</v>
       </c>
       <c r="C12">
-        <v>28.63733675900665</v>
+        <v>28.28646312668487</v>
       </c>
       <c r="D12">
-        <v>29.65273675900665</v>
+        <v>29.61540312668487</v>
       </c>
       <c r="E12">
-        <v>2.4814</v>
+        <v>2.79494</v>
       </c>
       <c r="F12">
-        <v>3.1354</v>
+        <v>3.44894</v>
       </c>
       <c r="G12">
         <v>2.12</v>
@@ -2271,45 +2271,45 @@
         <v>2.07</v>
       </c>
       <c r="M12">
-        <v>0.15771062</v>
+        <v>0.178655092</v>
       </c>
       <c r="N12">
-        <v>1.91228938</v>
+        <v>1.891344908</v>
       </c>
       <c r="O12">
-        <v>0.191228938</v>
+        <v>0.1891344908</v>
       </c>
       <c r="P12">
-        <v>1.721060442</v>
+        <v>1.7022104172</v>
       </c>
       <c r="Q12">
-        <v>2.351060442</v>
+        <v>2.3322104172</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1112620325467929</v>
+        <v>0.1119306947791401</v>
       </c>
       <c r="T12">
-        <v>1.012676824077748</v>
+        <v>1.023020816152086</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.1</v>
       </c>
       <c r="W12">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.12530506823193</v>
+        <v>11.58657151512928</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1047465183534347</v>
+        <v>0.1046952074147558</v>
       </c>
       <c r="C13">
-        <v>28.28646312668487</v>
+        <v>27.99580174267954</v>
       </c>
       <c r="D13">
-        <v>29.61540312668487</v>
+        <v>29.63828174267953</v>
       </c>
       <c r="E13">
-        <v>2.79494</v>
+        <v>3.10848</v>
       </c>
       <c r="F13">
-        <v>3.44894</v>
+        <v>3.76248</v>
       </c>
       <c r="G13">
         <v>2.12</v>
@@ -2353,28 +2353,28 @@
         <v>2.07</v>
       </c>
       <c r="M13">
-        <v>0.178655092</v>
+        <v>0.194896464</v>
       </c>
       <c r="N13">
-        <v>1.891344908</v>
+        <v>1.875103536</v>
       </c>
       <c r="O13">
-        <v>0.1891344908</v>
+        <v>0.1875103536</v>
       </c>
       <c r="P13">
-        <v>1.7022104172</v>
+        <v>1.6875931824</v>
       </c>
       <c r="Q13">
-        <v>2.3322104172</v>
+        <v>2.3175931824</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1119306947791401</v>
+        <v>0.1126145538804043</v>
       </c>
       <c r="T13">
-        <v>1.023020816152086</v>
+        <v>1.033599898955387</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.58657151512928</v>
+        <v>10.62102388886851</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1046952074147558</v>
+        <v>0.1048427964760769</v>
       </c>
       <c r="C14">
-        <v>27.99580174267954</v>
+        <v>27.61654963844779</v>
       </c>
       <c r="D14">
-        <v>29.63828174267953</v>
+        <v>29.57256963844779</v>
       </c>
       <c r="E14">
-        <v>3.10848</v>
+        <v>3.42202</v>
       </c>
       <c r="F14">
-        <v>3.76248</v>
+        <v>4.07602</v>
       </c>
       <c r="G14">
         <v>2.12</v>
@@ -2435,45 +2435,45 @@
         <v>2.07</v>
       </c>
       <c r="M14">
-        <v>0.194896464</v>
+        <v>0.21806707</v>
       </c>
       <c r="N14">
-        <v>1.875103536</v>
+        <v>1.85193293</v>
       </c>
       <c r="O14">
-        <v>0.1875103536</v>
+        <v>0.185193293</v>
       </c>
       <c r="P14">
-        <v>1.6875931824</v>
+        <v>1.666739637</v>
       </c>
       <c r="Q14">
-        <v>2.3175931824</v>
+        <v>2.296739637</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1126145538804043</v>
+        <v>0.1133141338805481</v>
       </c>
       <c r="T14">
-        <v>1.033599898955387</v>
+        <v>1.044422179064511</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>10.62102388886851</v>
+        <v>9.492492378606272</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1048427964760769</v>
+        <v>0.1048067855373979</v>
       </c>
       <c r="C15">
-        <v>27.61654963844779</v>
+        <v>27.31901614992651</v>
       </c>
       <c r="D15">
-        <v>29.57256963844779</v>
+        <v>29.58857614992651</v>
       </c>
       <c r="E15">
-        <v>3.42202</v>
+        <v>3.73556</v>
       </c>
       <c r="F15">
-        <v>4.07602</v>
+        <v>4.38956</v>
       </c>
       <c r="G15">
         <v>2.12</v>
@@ -2517,28 +2517,28 @@
         <v>2.07</v>
       </c>
       <c r="M15">
-        <v>0.21806707</v>
+        <v>0.23484146</v>
       </c>
       <c r="N15">
-        <v>1.85193293</v>
+        <v>1.83515854</v>
       </c>
       <c r="O15">
-        <v>0.185193293</v>
+        <v>0.183515854</v>
       </c>
       <c r="P15">
-        <v>1.666739637</v>
+        <v>1.651642686</v>
       </c>
       <c r="Q15">
-        <v>2.296739637</v>
+        <v>2.281642686</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1133141338805481</v>
+        <v>0.1140299831830209</v>
       </c>
       <c r="T15">
-        <v>1.044422179064511</v>
+        <v>1.055496140106405</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>9.492492378606272</v>
+        <v>8.814457208705823</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1048067855373979</v>
+        <v>0.1047707745987191</v>
       </c>
       <c r="C16">
-        <v>27.31901614992651</v>
+        <v>27.02149999822536</v>
       </c>
       <c r="D16">
-        <v>29.58857614992651</v>
+        <v>29.60459999822536</v>
       </c>
       <c r="E16">
-        <v>3.73556</v>
+        <v>4.049100000000001</v>
       </c>
       <c r="F16">
-        <v>4.38956</v>
+        <v>4.703100000000001</v>
       </c>
       <c r="G16">
         <v>2.12</v>
@@ -2599,28 +2599,28 @@
         <v>2.07</v>
       </c>
       <c r="M16">
-        <v>0.23484146</v>
+        <v>0.25161585</v>
       </c>
       <c r="N16">
-        <v>1.83515854</v>
+        <v>1.81838415</v>
       </c>
       <c r="O16">
-        <v>0.183515854</v>
+        <v>0.181838415</v>
       </c>
       <c r="P16">
-        <v>1.651642686</v>
+        <v>1.636545735</v>
       </c>
       <c r="Q16">
-        <v>2.281642686</v>
+        <v>2.266545735</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1140299831830209</v>
+        <v>0.114762675998493</v>
       </c>
       <c r="T16">
-        <v>1.055496140106405</v>
+        <v>1.06683066493752</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.814457208705823</v>
+        <v>8.226826728125435</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1047707745987191</v>
+        <v>0.1047347636600402</v>
       </c>
       <c r="C17">
-        <v>27.02149999822537</v>
+        <v>26.72400121152619</v>
       </c>
       <c r="D17">
-        <v>29.60459999822537</v>
+        <v>29.62064121152619</v>
       </c>
       <c r="E17">
-        <v>4.0491</v>
+        <v>4.36264</v>
       </c>
       <c r="F17">
-        <v>4.7031</v>
+        <v>5.01664</v>
       </c>
       <c r="G17">
         <v>2.12</v>
@@ -2681,28 +2681,28 @@
         <v>2.07</v>
       </c>
       <c r="M17">
-        <v>0.25161585</v>
+        <v>0.26839024</v>
       </c>
       <c r="N17">
-        <v>1.81838415</v>
+        <v>1.80160976</v>
       </c>
       <c r="O17">
-        <v>0.1818384150000001</v>
+        <v>0.180160976</v>
       </c>
       <c r="P17">
-        <v>1.636545735</v>
+        <v>1.621448784</v>
       </c>
       <c r="Q17">
-        <v>2.266545735</v>
+        <v>2.251448784</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.114762675998493</v>
+        <v>0.1155128138810002</v>
       </c>
       <c r="T17">
-        <v>1.06683066493752</v>
+        <v>1.078435059407471</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.226826728125436</v>
+        <v>7.712650057617595</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1047347636600402</v>
+        <v>0.1048211527213613</v>
       </c>
       <c r="C18">
-        <v>26.72400121152619</v>
+        <v>26.37200799955313</v>
       </c>
       <c r="D18">
-        <v>29.62064121152619</v>
+        <v>29.58218799955312</v>
       </c>
       <c r="E18">
-        <v>4.36264</v>
+        <v>4.67618</v>
       </c>
       <c r="F18">
-        <v>5.01664</v>
+        <v>5.33018</v>
       </c>
       <c r="G18">
         <v>2.12</v>
@@ -2763,45 +2763,45 @@
         <v>2.07</v>
       </c>
       <c r="M18">
-        <v>0.26839024</v>
+        <v>0.289428774</v>
       </c>
       <c r="N18">
-        <v>1.80160976</v>
+        <v>1.780571226</v>
       </c>
       <c r="O18">
-        <v>0.180160976</v>
+        <v>0.1780571226</v>
       </c>
       <c r="P18">
-        <v>1.621448784</v>
+        <v>1.6025141034</v>
       </c>
       <c r="Q18">
-        <v>2.251448784</v>
+        <v>2.2325141034</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1155128138810002</v>
+        <v>0.116281027375134</v>
       </c>
       <c r="T18">
-        <v>1.078435059407471</v>
+        <v>1.090319077840554</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.712650057617595</v>
+        <v>7.152018686296892</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1048211527213613</v>
+        <v>0.1047923417826823</v>
       </c>
       <c r="C19">
-        <v>26.37200799955313</v>
+        <v>26.07128112801151</v>
       </c>
       <c r="D19">
-        <v>29.58218799955312</v>
+        <v>29.59500112801151</v>
       </c>
       <c r="E19">
-        <v>4.67618</v>
+        <v>4.989720000000001</v>
       </c>
       <c r="F19">
-        <v>5.33018</v>
+        <v>5.643720000000001</v>
       </c>
       <c r="G19">
         <v>2.12</v>
@@ -2845,28 +2845,28 @@
         <v>2.07</v>
       </c>
       <c r="M19">
-        <v>0.289428774</v>
+        <v>0.3064539960000001</v>
       </c>
       <c r="N19">
-        <v>1.780571226</v>
+        <v>1.763546004</v>
       </c>
       <c r="O19">
-        <v>0.1780571226</v>
+        <v>0.1763546004</v>
       </c>
       <c r="P19">
-        <v>1.6025141034</v>
+        <v>1.5871914036</v>
       </c>
       <c r="Q19">
-        <v>2.2325141034</v>
+        <v>2.2171914036</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.116281027375134</v>
+        <v>0.117067977783759</v>
       </c>
       <c r="T19">
-        <v>1.090319077840554</v>
+        <v>1.10249295038176</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.152018686296892</v>
+        <v>6.754684314835953</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1047923417826824</v>
+        <v>0.1047635308440035</v>
       </c>
       <c r="C20">
-        <v>26.07128112801151</v>
+        <v>25.77056536094955</v>
       </c>
       <c r="D20">
-        <v>29.59500112801151</v>
+        <v>29.60782536094955</v>
       </c>
       <c r="E20">
-        <v>4.98972</v>
+        <v>5.30326</v>
       </c>
       <c r="F20">
-        <v>5.64372</v>
+        <v>5.95726</v>
       </c>
       <c r="G20">
         <v>2.12</v>
@@ -2927,28 +2927,28 @@
         <v>2.07</v>
       </c>
       <c r="M20">
-        <v>0.306453996</v>
+        <v>0.323479218</v>
       </c>
       <c r="N20">
-        <v>1.763546004</v>
+        <v>1.746520782</v>
       </c>
       <c r="O20">
-        <v>0.1763546004</v>
+        <v>0.1746520782</v>
       </c>
       <c r="P20">
-        <v>1.5871914036</v>
+        <v>1.5718687038</v>
       </c>
       <c r="Q20">
-        <v>2.2171914036</v>
+        <v>2.2018687038</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.117067977783759</v>
+        <v>0.1178743590666709</v>
       </c>
       <c r="T20">
-        <v>1.10249295038176</v>
+        <v>1.114967412368429</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.754684314835954</v>
+        <v>6.399174614055114</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1047635308440035</v>
+        <v>0.1049147199053246</v>
       </c>
       <c r="C21">
-        <v>25.77056536094955</v>
+        <v>25.38985215466131</v>
       </c>
       <c r="D21">
-        <v>29.60782536094955</v>
+        <v>29.54065215466131</v>
       </c>
       <c r="E21">
-        <v>5.30326</v>
+        <v>5.6168</v>
       </c>
       <c r="F21">
-        <v>5.95726</v>
+        <v>6.2708</v>
       </c>
       <c r="G21">
         <v>2.12</v>
@@ -3009,45 +3009,45 @@
         <v>2.07</v>
       </c>
       <c r="M21">
-        <v>0.323479218</v>
+        <v>0.34677524</v>
       </c>
       <c r="N21">
-        <v>1.746520782</v>
+        <v>1.72322476</v>
       </c>
       <c r="O21">
-        <v>0.1746520782</v>
+        <v>0.1723224760000001</v>
       </c>
       <c r="P21">
-        <v>1.5718687038</v>
+        <v>1.550902284</v>
       </c>
       <c r="Q21">
-        <v>2.2018687038</v>
+        <v>2.180902284</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1178743590666709</v>
+        <v>0.1187008998816557</v>
       </c>
       <c r="T21">
-        <v>1.114967412368429</v>
+        <v>1.127753735904764</v>
       </c>
       <c r="U21">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V21">
         <v>0.1</v>
       </c>
       <c r="W21">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y21">
-        <v>6.399174614055114</v>
+        <v>5.969284312224829</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1049147199053246</v>
+        <v>0.1048949089666457</v>
       </c>
       <c r="C22">
-        <v>25.38985215466131</v>
+        <v>25.08509678434599</v>
       </c>
       <c r="D22">
-        <v>29.54065215466131</v>
+        <v>29.54943678434599</v>
       </c>
       <c r="E22">
-        <v>5.6168</v>
+        <v>5.93034</v>
       </c>
       <c r="F22">
-        <v>6.2708</v>
+        <v>6.58434</v>
       </c>
       <c r="G22">
         <v>2.12</v>
@@ -3091,28 +3091,28 @@
         <v>2.07</v>
       </c>
       <c r="M22">
-        <v>0.34677524</v>
+        <v>0.364114002</v>
       </c>
       <c r="N22">
-        <v>1.72322476</v>
+        <v>1.705885998</v>
       </c>
       <c r="O22">
-        <v>0.1723224760000001</v>
+        <v>0.1705885998</v>
       </c>
       <c r="P22">
-        <v>1.550902284</v>
+        <v>1.5352973982</v>
       </c>
       <c r="Q22">
-        <v>2.180902284</v>
+        <v>2.1652973982</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1187008998816557</v>
+        <v>0.1195483657805641</v>
       </c>
       <c r="T22">
-        <v>1.127753735904764</v>
+        <v>1.140863763834424</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.969284312224829</v>
+        <v>5.685032678309362</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1048949089666457</v>
+        <v>0.1048750980279668</v>
       </c>
       <c r="C23">
-        <v>25.08509678434599</v>
+        <v>24.78034664023037</v>
       </c>
       <c r="D23">
-        <v>29.54943678434599</v>
+        <v>29.55822664023037</v>
       </c>
       <c r="E23">
-        <v>5.930339999999999</v>
+        <v>6.24388</v>
       </c>
       <c r="F23">
-        <v>6.584339999999999</v>
+        <v>6.89788</v>
       </c>
       <c r="G23">
         <v>2.12</v>
@@ -3173,28 +3173,28 @@
         <v>2.07</v>
       </c>
       <c r="M23">
-        <v>0.364114002</v>
+        <v>0.381452764</v>
       </c>
       <c r="N23">
-        <v>1.705885998</v>
+        <v>1.688547236</v>
       </c>
       <c r="O23">
-        <v>0.1705885998</v>
+        <v>0.1688547236</v>
       </c>
       <c r="P23">
-        <v>1.5352973982</v>
+        <v>1.5196925124</v>
       </c>
       <c r="Q23">
-        <v>2.1652973982</v>
+        <v>2.1496925124</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1195483657805641</v>
+        <v>0.1204175615743164</v>
       </c>
       <c r="T23">
-        <v>1.140863763834424</v>
+        <v>1.154309946326383</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.685032678309362</v>
+        <v>5.426622102022573</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1048750980279668</v>
+        <v>0.1048552870892878</v>
       </c>
       <c r="C24">
-        <v>24.78034664023037</v>
+        <v>24.47560172697965</v>
       </c>
       <c r="D24">
-        <v>29.55822664023037</v>
+        <v>29.56702172697965</v>
       </c>
       <c r="E24">
-        <v>6.24388</v>
+        <v>6.55742</v>
       </c>
       <c r="F24">
-        <v>6.89788</v>
+        <v>7.21142</v>
       </c>
       <c r="G24">
         <v>2.12</v>
@@ -3255,28 +3255,28 @@
         <v>2.07</v>
       </c>
       <c r="M24">
-        <v>0.381452764</v>
+        <v>0.3987915260000001</v>
       </c>
       <c r="N24">
-        <v>1.688547236</v>
+        <v>1.671208474</v>
       </c>
       <c r="O24">
-        <v>0.1688547236</v>
+        <v>0.1671208474</v>
       </c>
       <c r="P24">
-        <v>1.5196925124</v>
+        <v>1.5040876266</v>
       </c>
       <c r="Q24">
-        <v>2.1496925124</v>
+        <v>2.1340876266</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1204175615743164</v>
+        <v>0.121309333882192</v>
       </c>
       <c r="T24">
-        <v>1.154309946326383</v>
+        <v>1.16810538031164</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.426622102022573</v>
+        <v>5.190682010630286</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1048552870892878</v>
+        <v>0.104835476150609</v>
       </c>
       <c r="C25">
-        <v>24.47560172697965</v>
+        <v>24.17086204926455</v>
       </c>
       <c r="D25">
-        <v>29.56702172697965</v>
+        <v>29.57582204926455</v>
       </c>
       <c r="E25">
-        <v>6.55742</v>
+        <v>6.87096</v>
       </c>
       <c r="F25">
-        <v>7.21142</v>
+        <v>7.52496</v>
       </c>
       <c r="G25">
         <v>2.12</v>
@@ -3337,28 +3337,28 @@
         <v>2.07</v>
       </c>
       <c r="M25">
-        <v>0.3987915260000001</v>
+        <v>0.416130288</v>
       </c>
       <c r="N25">
-        <v>1.671208474</v>
+        <v>1.653869712</v>
       </c>
       <c r="O25">
-        <v>0.1671208474</v>
+        <v>0.1653869712</v>
       </c>
       <c r="P25">
-        <v>1.5040876266</v>
+        <v>1.4884827408</v>
       </c>
       <c r="Q25">
-        <v>2.1340876266</v>
+        <v>2.1184827408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.121309333882192</v>
+        <v>0.1222245738823802</v>
       </c>
       <c r="T25">
-        <v>1.16810538031164</v>
+        <v>1.182263852033351</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.190682010630286</v>
+        <v>4.974403593520691</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.104835476150609</v>
+        <v>0.10481566521193</v>
       </c>
       <c r="C26">
-        <v>24.17086204926455</v>
+        <v>23.8661276117614</v>
       </c>
       <c r="D26">
-        <v>29.57582204926455</v>
+        <v>29.5846276117614</v>
       </c>
       <c r="E26">
-        <v>6.870959999999999</v>
+        <v>7.1845</v>
       </c>
       <c r="F26">
-        <v>7.524959999999999</v>
+        <v>7.8385</v>
       </c>
       <c r="G26">
         <v>2.12</v>
@@ -3419,28 +3419,28 @@
         <v>2.07</v>
       </c>
       <c r="M26">
-        <v>0.416130288</v>
+        <v>0.43346905</v>
       </c>
       <c r="N26">
-        <v>1.653869712</v>
+        <v>1.63653095</v>
       </c>
       <c r="O26">
-        <v>0.1653869712</v>
+        <v>0.163653095</v>
       </c>
       <c r="P26">
-        <v>1.4884827408</v>
+        <v>1.472877855</v>
       </c>
       <c r="Q26">
-        <v>2.1184827408</v>
+        <v>2.102877855</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1222245738823802</v>
+        <v>0.1231642202825734</v>
       </c>
       <c r="T26">
-        <v>1.182263852033351</v>
+        <v>1.196799883000974</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.974403593520692</v>
+        <v>4.775427449779864</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.10481566521193</v>
+        <v>0.1047958542732511</v>
       </c>
       <c r="C27">
-        <v>23.8661276117614</v>
+        <v>23.56139841915206</v>
       </c>
       <c r="D27">
-        <v>29.5846276117614</v>
+        <v>29.59343841915205</v>
       </c>
       <c r="E27">
-        <v>7.1845</v>
+        <v>7.49804</v>
       </c>
       <c r="F27">
-        <v>7.8385</v>
+        <v>8.15204</v>
       </c>
       <c r="G27">
         <v>2.12</v>
@@ -3501,28 +3501,28 @@
         <v>2.07</v>
       </c>
       <c r="M27">
-        <v>0.43346905</v>
+        <v>0.450807812</v>
       </c>
       <c r="N27">
-        <v>1.63653095</v>
+        <v>1.619192188</v>
       </c>
       <c r="O27">
-        <v>0.163653095</v>
+        <v>0.1619192188</v>
       </c>
       <c r="P27">
-        <v>1.472877855</v>
+        <v>1.4572729692</v>
       </c>
       <c r="Q27">
-        <v>2.102877855</v>
+        <v>2.0872729692</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1231642202825734</v>
+        <v>0.1241292625314205</v>
       </c>
       <c r="T27">
-        <v>1.196799883000974</v>
+        <v>1.211728779670425</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.775427449779864</v>
+        <v>4.59175716324987</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1047958542732511</v>
+        <v>0.1053835433345722</v>
       </c>
       <c r="C28">
-        <v>23.56139841915206</v>
+        <v>22.98869866032737</v>
       </c>
       <c r="D28">
-        <v>29.59343841915205</v>
+        <v>29.33427866032737</v>
       </c>
       <c r="E28">
-        <v>7.49804</v>
+        <v>7.811580000000001</v>
       </c>
       <c r="F28">
-        <v>8.15204</v>
+        <v>8.465580000000001</v>
       </c>
       <c r="G28">
         <v>2.12</v>
@@ -3583,45 +3583,45 @@
         <v>2.07</v>
       </c>
       <c r="M28">
-        <v>0.450807812</v>
+        <v>0.4893105240000001</v>
       </c>
       <c r="N28">
-        <v>1.619192188</v>
+        <v>1.580689476</v>
       </c>
       <c r="O28">
-        <v>0.1619192188</v>
+        <v>0.1580689476</v>
       </c>
       <c r="P28">
-        <v>1.4572729692</v>
+        <v>1.4226205284</v>
       </c>
       <c r="Q28">
-        <v>2.0872729692</v>
+        <v>2.0526205284</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1241292625314205</v>
+        <v>0.1251207442939346</v>
       </c>
       <c r="T28">
-        <v>1.211728779670425</v>
+        <v>1.227066687207532</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.1</v>
       </c>
       <c r="W28">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.59175716324987</v>
+        <v>4.230442425554697</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1053835433345722</v>
+        <v>0.1053862323958933</v>
       </c>
       <c r="C29">
-        <v>22.98869866032737</v>
+        <v>22.67398326692447</v>
       </c>
       <c r="D29">
-        <v>29.33427866032737</v>
+        <v>29.33310326692446</v>
       </c>
       <c r="E29">
-        <v>7.811580000000001</v>
+        <v>8.125120000000001</v>
       </c>
       <c r="F29">
-        <v>8.465580000000001</v>
+        <v>8.779120000000001</v>
       </c>
       <c r="G29">
         <v>2.12</v>
@@ -3665,28 +3665,28 @@
         <v>2.07</v>
       </c>
       <c r="M29">
-        <v>0.4893105240000001</v>
+        <v>0.5074331360000001</v>
       </c>
       <c r="N29">
-        <v>1.580689476</v>
+        <v>1.562566864</v>
       </c>
       <c r="O29">
-        <v>0.1580689476</v>
+        <v>0.1562566864</v>
       </c>
       <c r="P29">
-        <v>1.4226205284</v>
+        <v>1.4063101776</v>
       </c>
       <c r="Q29">
-        <v>2.0526205284</v>
+        <v>2.0363101776</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1251207442939346</v>
+        <v>0.1261397672165185</v>
       </c>
       <c r="T29">
-        <v>1.227066687207532</v>
+        <v>1.242830647731781</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.230442425554697</v>
+        <v>4.079355196070601</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1053862323958933</v>
+        <v>0.1063024214572144</v>
       </c>
       <c r="C30">
-        <v>22.67398326692447</v>
+        <v>21.96538476183417</v>
       </c>
       <c r="D30">
-        <v>29.33310326692446</v>
+        <v>28.93804476183417</v>
       </c>
       <c r="E30">
-        <v>8.125120000000001</v>
+        <v>8.43866</v>
       </c>
       <c r="F30">
-        <v>8.779120000000001</v>
+        <v>9.09266</v>
       </c>
       <c r="G30">
         <v>2.12</v>
@@ -3747,45 +3747,45 @@
         <v>2.07</v>
       </c>
       <c r="M30">
-        <v>0.5074331360000001</v>
+        <v>0.557380058</v>
       </c>
       <c r="N30">
-        <v>1.562566864</v>
+        <v>1.512619942</v>
       </c>
       <c r="O30">
-        <v>0.1562566864</v>
+        <v>0.1512619942</v>
       </c>
       <c r="P30">
-        <v>1.4063101776</v>
+        <v>1.3613579478</v>
       </c>
       <c r="Q30">
-        <v>2.0363101776</v>
+        <v>1.9913579478</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1261397672165185</v>
+        <v>0.1271874950101612</v>
       </c>
       <c r="T30">
-        <v>1.242830647731781</v>
+        <v>1.259038663482065</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.1</v>
       </c>
       <c r="W30">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.079355196070601</v>
+        <v>3.713803481645194</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1063024214572144</v>
+        <v>0.1063366105185355</v>
       </c>
       <c r="C31">
-        <v>21.96538476183419</v>
+        <v>21.63730837569848</v>
       </c>
       <c r="D31">
-        <v>28.93804476183419</v>
+        <v>28.92350837569848</v>
       </c>
       <c r="E31">
-        <v>8.438659999999999</v>
+        <v>8.7522</v>
       </c>
       <c r="F31">
-        <v>9.092659999999999</v>
+        <v>9.4062</v>
       </c>
       <c r="G31">
         <v>2.12</v>
@@ -3829,28 +3829,28 @@
         <v>2.07</v>
       </c>
       <c r="M31">
-        <v>0.5573800579999999</v>
+        <v>0.57660006</v>
       </c>
       <c r="N31">
-        <v>1.512619942</v>
+        <v>1.49339994</v>
       </c>
       <c r="O31">
-        <v>0.1512619942000001</v>
+        <v>0.149339994</v>
       </c>
       <c r="P31">
-        <v>1.3613579478</v>
+        <v>1.344059946</v>
       </c>
       <c r="Q31">
-        <v>1.991357947800001</v>
+        <v>1.974059946</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1271874950101612</v>
+        <v>0.1282651578836222</v>
       </c>
       <c r="T31">
-        <v>1.259038663482065</v>
+        <v>1.275709765396643</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.713803481645195</v>
+        <v>3.590010032257021</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1063366105185355</v>
+        <v>0.1071519995798566</v>
       </c>
       <c r="C32">
-        <v>21.63730837569848</v>
+        <v>20.98136036579258</v>
       </c>
       <c r="D32">
-        <v>28.92350837569848</v>
+        <v>28.58110036579258</v>
       </c>
       <c r="E32">
-        <v>8.7522</v>
+        <v>9.06574</v>
       </c>
       <c r="F32">
-        <v>9.4062</v>
+        <v>9.71974</v>
       </c>
       <c r="G32">
         <v>2.12</v>
@@ -3911,45 +3911,45 @@
         <v>2.07</v>
       </c>
       <c r="M32">
-        <v>0.57660006</v>
+        <v>0.623035334</v>
       </c>
       <c r="N32">
-        <v>1.49339994</v>
+        <v>1.446964666</v>
       </c>
       <c r="O32">
-        <v>0.149339994</v>
+        <v>0.1446964666</v>
       </c>
       <c r="P32">
-        <v>1.344059946</v>
+        <v>1.3022681994</v>
       </c>
       <c r="Q32">
-        <v>1.974059946</v>
+        <v>1.9322681994</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1282651578836222</v>
+        <v>0.1293740573621111</v>
       </c>
       <c r="T32">
-        <v>1.275709765396643</v>
+        <v>1.292864087656571</v>
       </c>
       <c r="U32">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V32">
         <v>0.1</v>
       </c>
       <c r="W32">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.590010032257021</v>
+        <v>3.322443988385417</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1071519995798566</v>
+        <v>0.1072113886411777</v>
       </c>
       <c r="C33">
-        <v>20.98136036579258</v>
+        <v>20.64319746817092</v>
       </c>
       <c r="D33">
-        <v>28.58110036579258</v>
+        <v>28.55647746817091</v>
       </c>
       <c r="E33">
-        <v>9.06574</v>
+        <v>9.37928</v>
       </c>
       <c r="F33">
-        <v>9.71974</v>
+        <v>10.03328</v>
       </c>
       <c r="G33">
         <v>2.12</v>
@@ -3993,28 +3993,28 @@
         <v>2.07</v>
       </c>
       <c r="M33">
-        <v>0.623035334</v>
+        <v>0.643133248</v>
       </c>
       <c r="N33">
-        <v>1.446964666</v>
+        <v>1.426866752</v>
       </c>
       <c r="O33">
-        <v>0.1446964666</v>
+        <v>0.1426866752</v>
       </c>
       <c r="P33">
-        <v>1.3022681994</v>
+        <v>1.2841800768</v>
       </c>
       <c r="Q33">
-        <v>1.9322681994</v>
+        <v>1.9141800768</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1293740573621111</v>
+        <v>0.1305155715311437</v>
       </c>
       <c r="T33">
-        <v>1.292864087656571</v>
+        <v>1.310522948806497</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.322443988385417</v>
+        <v>3.218617613748372</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1072113886411777</v>
+        <v>0.1072707777024988</v>
       </c>
       <c r="C34">
-        <v>20.64319746817092</v>
+        <v>20.30507695976498</v>
       </c>
       <c r="D34">
-        <v>28.55647746817091</v>
+        <v>28.53189695976498</v>
       </c>
       <c r="E34">
-        <v>9.37928</v>
+        <v>9.692820000000001</v>
       </c>
       <c r="F34">
-        <v>10.03328</v>
+        <v>10.34682</v>
       </c>
       <c r="G34">
         <v>2.12</v>
@@ -4075,28 +4075,28 @@
         <v>2.07</v>
       </c>
       <c r="M34">
-        <v>0.643133248</v>
+        <v>0.6632311620000001</v>
       </c>
       <c r="N34">
-        <v>1.426866752</v>
+        <v>1.406768838</v>
       </c>
       <c r="O34">
-        <v>0.1426866752</v>
+        <v>0.1406768838</v>
       </c>
       <c r="P34">
-        <v>1.2841800768</v>
+        <v>1.2660919542</v>
       </c>
       <c r="Q34">
-        <v>1.9141800768</v>
+        <v>1.8960919542</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1305155715311437</v>
+        <v>0.1316911607499982</v>
       </c>
       <c r="T34">
-        <v>1.310522948806497</v>
+        <v>1.328708940140002</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.218617613748372</v>
+        <v>3.121083746665088</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1072707777024988</v>
+        <v>0.1073301667638199</v>
       </c>
       <c r="C35">
-        <v>20.30507695976498</v>
+        <v>19.96699873120703</v>
       </c>
       <c r="D35">
-        <v>28.53189695976498</v>
+        <v>28.50735873120703</v>
       </c>
       <c r="E35">
-        <v>9.692820000000001</v>
+        <v>10.00636</v>
       </c>
       <c r="F35">
-        <v>10.34682</v>
+        <v>10.66036</v>
       </c>
       <c r="G35">
         <v>2.12</v>
@@ -4157,28 +4157,28 @@
         <v>2.07</v>
       </c>
       <c r="M35">
-        <v>0.6632311620000001</v>
+        <v>0.6833290760000001</v>
       </c>
       <c r="N35">
-        <v>1.406768838</v>
+        <v>1.386670924</v>
       </c>
       <c r="O35">
-        <v>0.1406768838</v>
+        <v>0.1386670924</v>
       </c>
       <c r="P35">
-        <v>1.2660919542</v>
+        <v>1.2480038316</v>
       </c>
       <c r="Q35">
-        <v>1.8960919542</v>
+        <v>1.8780038316</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1316911607499982</v>
+        <v>0.1329023738845757</v>
       </c>
       <c r="T35">
-        <v>1.328708940140002</v>
+        <v>1.347446022119978</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.121083746665088</v>
+        <v>3.029287165880821</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1073301667638199</v>
+        <v>0.109846555825141</v>
       </c>
       <c r="C36">
-        <v>19.96699873120703</v>
+        <v>18.65116154969214</v>
       </c>
       <c r="D36">
-        <v>28.50735873120703</v>
+        <v>27.50506154969214</v>
       </c>
       <c r="E36">
-        <v>10.00636</v>
+        <v>10.3199</v>
       </c>
       <c r="F36">
-        <v>10.66036</v>
+        <v>10.9739</v>
       </c>
       <c r="G36">
         <v>2.12</v>
@@ -4239,45 +4239,45 @@
         <v>2.07</v>
       </c>
       <c r="M36">
-        <v>0.6833290760000001</v>
+        <v>0.7890234100000001</v>
       </c>
       <c r="N36">
-        <v>1.386670924</v>
+        <v>1.28097659</v>
       </c>
       <c r="O36">
-        <v>0.1386670924</v>
+        <v>0.128097659</v>
       </c>
       <c r="P36">
-        <v>1.2480038316</v>
+        <v>1.152878931</v>
       </c>
       <c r="Q36">
-        <v>1.8780038316</v>
+        <v>1.782878931</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1329023738845757</v>
+        <v>0.1341508551156016</v>
       </c>
       <c r="T36">
-        <v>1.347446022119978</v>
+        <v>1.366759629699337</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.1</v>
       </c>
       <c r="W36">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.029287165880821</v>
+        <v>2.623496304121065</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.109846555825141</v>
+        <v>0.1099761448864621</v>
       </c>
       <c r="C37">
-        <v>18.65116154969214</v>
+        <v>18.28791002671072</v>
       </c>
       <c r="D37">
-        <v>27.50506154969214</v>
+        <v>27.45535002671072</v>
       </c>
       <c r="E37">
-        <v>10.3199</v>
+        <v>10.63344</v>
       </c>
       <c r="F37">
-        <v>10.9739</v>
+        <v>11.28744</v>
       </c>
       <c r="G37">
         <v>2.12</v>
@@ -4321,28 +4321,28 @@
         <v>2.07</v>
       </c>
       <c r="M37">
-        <v>0.7890234100000001</v>
+        <v>0.8115669360000002</v>
       </c>
       <c r="N37">
-        <v>1.28097659</v>
+        <v>1.258433064</v>
       </c>
       <c r="O37">
-        <v>0.128097659</v>
+        <v>0.1258433064</v>
       </c>
       <c r="P37">
-        <v>1.152878931</v>
+        <v>1.1325897576</v>
       </c>
       <c r="Q37">
-        <v>1.782878931</v>
+        <v>1.7625897576</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1341508551156016</v>
+        <v>0.135438351385097</v>
       </c>
       <c r="T37">
-        <v>1.366759629699337</v>
+        <v>1.386676787515552</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.623496304121065</v>
+        <v>2.550621406784369</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1099761448864621</v>
+        <v>0.1114044339477832</v>
       </c>
       <c r="C38">
-        <v>18.28791002671072</v>
+        <v>17.4381376479248</v>
       </c>
       <c r="D38">
-        <v>27.45535002671072</v>
+        <v>26.9191176479248</v>
       </c>
       <c r="E38">
-        <v>10.63344</v>
+        <v>10.94698</v>
       </c>
       <c r="F38">
-        <v>11.28744</v>
+        <v>11.60098</v>
       </c>
       <c r="G38">
         <v>2.12</v>
@@ -4403,45 +4403,45 @@
         <v>2.07</v>
       </c>
       <c r="M38">
-        <v>0.8115669360000001</v>
+        <v>0.879354284</v>
       </c>
       <c r="N38">
-        <v>1.258433064</v>
+        <v>1.190645716</v>
       </c>
       <c r="O38">
-        <v>0.1258433064</v>
+        <v>0.1190645716</v>
       </c>
       <c r="P38">
-        <v>1.1325897576</v>
+        <v>1.0715811444</v>
       </c>
       <c r="Q38">
-        <v>1.7625897576</v>
+        <v>1.7015811444</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.135438351385097</v>
+        <v>0.1367667205520368</v>
       </c>
       <c r="T38">
-        <v>1.386676787515552</v>
+        <v>1.407226236056091</v>
       </c>
       <c r="U38">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V38">
         <v>0.1</v>
       </c>
       <c r="W38">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y38">
-        <v>2.550621406784369</v>
+        <v>2.354000017585631</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1114044339477832</v>
+        <v>0.1115691230091043</v>
       </c>
       <c r="C39">
-        <v>17.4381376479248</v>
+        <v>17.06411113220689</v>
       </c>
       <c r="D39">
-        <v>26.9191176479248</v>
+        <v>26.85863113220689</v>
       </c>
       <c r="E39">
-        <v>10.94698</v>
+        <v>11.26052</v>
       </c>
       <c r="F39">
-        <v>11.60098</v>
+        <v>11.91452</v>
       </c>
       <c r="G39">
         <v>2.12</v>
@@ -4485,28 +4485,28 @@
         <v>2.07</v>
       </c>
       <c r="M39">
-        <v>0.879354284</v>
+        <v>0.903120616</v>
       </c>
       <c r="N39">
-        <v>1.190645716</v>
+        <v>1.166879384</v>
       </c>
       <c r="O39">
-        <v>0.1190645716</v>
+        <v>0.1166879384</v>
       </c>
       <c r="P39">
-        <v>1.0715811444</v>
+        <v>1.0501914456</v>
       </c>
       <c r="Q39">
-        <v>1.7015811444</v>
+        <v>1.6801914456</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1367667205520368</v>
+        <v>0.138137940337265</v>
       </c>
       <c r="T39">
-        <v>1.407226236056091</v>
+        <v>1.428438570033421</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.354000017585631</v>
+        <v>2.292052648701799</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1115691230091043</v>
+        <v>0.1117338120704254</v>
       </c>
       <c r="C40">
-        <v>17.06411113220689</v>
+        <v>16.69035583014812</v>
       </c>
       <c r="D40">
-        <v>26.85863113220689</v>
+        <v>26.79841583014812</v>
       </c>
       <c r="E40">
-        <v>11.26052</v>
+        <v>11.57406</v>
       </c>
       <c r="F40">
-        <v>11.91452</v>
+        <v>12.22806</v>
       </c>
       <c r="G40">
         <v>2.12</v>
@@ -4567,28 +4567,28 @@
         <v>2.07</v>
       </c>
       <c r="M40">
-        <v>0.903120616</v>
+        <v>0.926886948</v>
       </c>
       <c r="N40">
-        <v>1.166879384</v>
+        <v>1.143113052</v>
       </c>
       <c r="O40">
-        <v>0.1166879384</v>
+        <v>0.1143113052</v>
       </c>
       <c r="P40">
-        <v>1.0501914456</v>
+        <v>1.0288017468</v>
       </c>
       <c r="Q40">
-        <v>1.6801914456</v>
+        <v>1.6588017468</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.138137940337265</v>
+        <v>0.1395541181482384</v>
       </c>
       <c r="T40">
-        <v>1.428438570033421</v>
+        <v>1.450346390370663</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.292052648701799</v>
+        <v>2.233282067965855</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1117338120704254</v>
+        <v>0.1118985011317465</v>
       </c>
       <c r="C41">
-        <v>16.69035583014812</v>
+        <v>16.31686992169884</v>
       </c>
       <c r="D41">
-        <v>26.79841583014812</v>
+        <v>26.73846992169884</v>
       </c>
       <c r="E41">
-        <v>11.57406</v>
+        <v>11.8876</v>
       </c>
       <c r="F41">
-        <v>12.22806</v>
+        <v>12.5416</v>
       </c>
       <c r="G41">
         <v>2.12</v>
@@ -4649,28 +4649,28 @@
         <v>2.07</v>
       </c>
       <c r="M41">
-        <v>0.926886948</v>
+        <v>0.9506532800000002</v>
       </c>
       <c r="N41">
-        <v>1.143113052</v>
+        <v>1.11934672</v>
       </c>
       <c r="O41">
-        <v>0.1143113052</v>
+        <v>0.111934672</v>
       </c>
       <c r="P41">
-        <v>1.0288017468</v>
+        <v>1.007412048</v>
       </c>
       <c r="Q41">
-        <v>1.6588017468</v>
+        <v>1.637412048</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1395541181482384</v>
+        <v>0.1410175018862442</v>
       </c>
       <c r="T41">
-        <v>1.450346390370663</v>
+        <v>1.472984471385814</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.233282067965855</v>
+        <v>2.177450016266709</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1118985011317465</v>
+        <v>0.1120631901930676</v>
       </c>
       <c r="C42">
-        <v>16.31686992169884</v>
+        <v>15.94365160305825</v>
       </c>
       <c r="D42">
-        <v>26.73846992169884</v>
+        <v>26.67879160305825</v>
       </c>
       <c r="E42">
-        <v>11.8876</v>
+        <v>12.20114</v>
       </c>
       <c r="F42">
-        <v>12.5416</v>
+        <v>12.85514</v>
       </c>
       <c r="G42">
         <v>2.12</v>
@@ -4731,28 +4731,28 @@
         <v>2.07</v>
       </c>
       <c r="M42">
-        <v>0.9506532800000002</v>
+        <v>0.9744196120000002</v>
       </c>
       <c r="N42">
-        <v>1.11934672</v>
+        <v>1.095580388</v>
       </c>
       <c r="O42">
-        <v>0.111934672</v>
+        <v>0.1095580388</v>
       </c>
       <c r="P42">
-        <v>1.007412048</v>
+        <v>0.9860223492000001</v>
       </c>
       <c r="Q42">
-        <v>1.637412048</v>
+        <v>1.6160223492</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1410175018862442</v>
+        <v>0.142530491852657</v>
       </c>
       <c r="T42">
-        <v>1.472984471385814</v>
+        <v>1.49638994497775</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.177450016266709</v>
+        <v>2.124341479284594</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1120631901930676</v>
+        <v>0.1122278792543887</v>
       </c>
       <c r="C43">
-        <v>15.94365160305825</v>
+        <v>15.57069908649353</v>
       </c>
       <c r="D43">
-        <v>26.67879160305825</v>
+        <v>26.61937908649353</v>
       </c>
       <c r="E43">
-        <v>12.20114</v>
+        <v>12.51468</v>
       </c>
       <c r="F43">
-        <v>12.85514</v>
+        <v>13.16868</v>
       </c>
       <c r="G43">
         <v>2.12</v>
@@ -4813,28 +4813,28 @@
         <v>2.07</v>
       </c>
       <c r="M43">
-        <v>0.9744196120000002</v>
+        <v>0.998185944</v>
       </c>
       <c r="N43">
-        <v>1.095580388</v>
+        <v>1.071814056</v>
       </c>
       <c r="O43">
-        <v>0.1095580388</v>
+        <v>0.1071814056</v>
       </c>
       <c r="P43">
-        <v>0.9860223492000001</v>
+        <v>0.9646326504000002</v>
       </c>
       <c r="Q43">
-        <v>1.6160223492</v>
+        <v>1.5946326504</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.142530491852657</v>
+        <v>0.1440956538868771</v>
       </c>
       <c r="T43">
-        <v>1.49638994497775</v>
+        <v>1.520602503865959</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.124341479284594</v>
+        <v>2.073761920254008</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1122278792543887</v>
+        <v>0.1123925683157098</v>
       </c>
       <c r="C44">
-        <v>15.57069908649353</v>
+        <v>15.19801060016126</v>
       </c>
       <c r="D44">
-        <v>26.61937908649353</v>
+        <v>26.56023060016125</v>
       </c>
       <c r="E44">
-        <v>12.51468</v>
+        <v>12.82822</v>
       </c>
       <c r="F44">
-        <v>13.16868</v>
+        <v>13.48222</v>
       </c>
       <c r="G44">
         <v>2.12</v>
@@ -4895,28 +4895,28 @@
         <v>2.07</v>
       </c>
       <c r="M44">
-        <v>0.9981859439999999</v>
+        <v>1.021952276</v>
       </c>
       <c r="N44">
-        <v>1.071814056</v>
+        <v>1.048047724</v>
       </c>
       <c r="O44">
-        <v>0.1071814056000001</v>
+        <v>0.1048047724</v>
       </c>
       <c r="P44">
-        <v>0.9646326504000005</v>
+        <v>0.9432429516</v>
       </c>
       <c r="Q44">
-        <v>1.5946326504</v>
+        <v>1.5732429516</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1440956538868771</v>
+        <v>0.1457157338872102</v>
       </c>
       <c r="T44">
-        <v>1.520602503865959</v>
+        <v>1.54566462622393</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.073761920254009</v>
+        <v>2.025534898852752</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1123925683157098</v>
+        <v>0.1181804573770309</v>
       </c>
       <c r="C45">
-        <v>15.19801060016126</v>
+        <v>12.9605924324646</v>
       </c>
       <c r="D45">
-        <v>26.56023060016125</v>
+        <v>24.6363524324646</v>
       </c>
       <c r="E45">
-        <v>12.82822</v>
+        <v>13.14176</v>
       </c>
       <c r="F45">
-        <v>13.48222</v>
+        <v>13.79576</v>
       </c>
       <c r="G45">
         <v>2.12</v>
@@ -4977,45 +4977,45 @@
         <v>2.07</v>
       </c>
       <c r="M45">
-        <v>1.021952276</v>
+        <v>1.2416184</v>
       </c>
       <c r="N45">
-        <v>1.048047724</v>
+        <v>0.8283816000000004</v>
       </c>
       <c r="O45">
-        <v>0.1048047724</v>
+        <v>0.08283816000000005</v>
       </c>
       <c r="P45">
-        <v>0.9432429516</v>
+        <v>0.7455434400000003</v>
       </c>
       <c r="Q45">
-        <v>1.5732429516</v>
+        <v>1.37554344</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1457157338872102</v>
+        <v>0.1473936738875552</v>
       </c>
       <c r="T45">
-        <v>1.54566462622393</v>
+        <v>1.5716218243804</v>
       </c>
       <c r="U45">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V45">
         <v>0.1</v>
       </c>
       <c r="W45">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>2.025534898852752</v>
+        <v>1.667178901343602</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1181804573770309</v>
+        <v>0.118472946438352</v>
       </c>
       <c r="C46">
-        <v>12.9605924324646</v>
+        <v>12.55720105273699</v>
       </c>
       <c r="D46">
-        <v>24.6363524324646</v>
+        <v>24.54650105273699</v>
       </c>
       <c r="E46">
-        <v>13.14176</v>
+        <v>13.4553</v>
       </c>
       <c r="F46">
-        <v>13.79576</v>
+        <v>14.1093</v>
       </c>
       <c r="G46">
         <v>2.12</v>
@@ -5059,28 +5059,28 @@
         <v>2.07</v>
       </c>
       <c r="M46">
-        <v>1.2416184</v>
+        <v>1.269837</v>
       </c>
       <c r="N46">
-        <v>0.8283816000000004</v>
+        <v>0.8001630000000004</v>
       </c>
       <c r="O46">
-        <v>0.08283816000000005</v>
+        <v>0.08001630000000004</v>
       </c>
       <c r="P46">
-        <v>0.7455434400000003</v>
+        <v>0.7201467000000004</v>
       </c>
       <c r="Q46">
-        <v>1.37554344</v>
+        <v>1.3501467</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1473936738875552</v>
+        <v>0.1491326298879127</v>
       </c>
       <c r="T46">
-        <v>1.5716218243804</v>
+        <v>1.598522920651651</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.667178901343602</v>
+        <v>1.630130481313744</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.118472946438352</v>
+        <v>0.1187654354996731</v>
       </c>
       <c r="C47">
-        <v>12.55720105273699</v>
+        <v>12.15446268634699</v>
       </c>
       <c r="D47">
-        <v>24.54650105273699</v>
+        <v>24.45730268634698</v>
       </c>
       <c r="E47">
-        <v>13.4553</v>
+        <v>13.76884</v>
       </c>
       <c r="F47">
-        <v>14.1093</v>
+        <v>14.42284</v>
       </c>
       <c r="G47">
         <v>2.12</v>
@@ -5141,28 +5141,28 @@
         <v>2.07</v>
       </c>
       <c r="M47">
-        <v>1.269837</v>
+        <v>1.2980556</v>
       </c>
       <c r="N47">
-        <v>0.8001630000000004</v>
+        <v>0.7719444000000002</v>
       </c>
       <c r="O47">
-        <v>0.08001630000000004</v>
+        <v>0.07719444000000003</v>
       </c>
       <c r="P47">
-        <v>0.7201467000000004</v>
+        <v>0.6947499600000002</v>
       </c>
       <c r="Q47">
-        <v>1.3501467</v>
+        <v>1.32474996</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1491326298879127</v>
+        <v>0.1509359916660613</v>
       </c>
       <c r="T47">
-        <v>1.598522920651651</v>
+        <v>1.626420353821837</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.630130481313744</v>
+        <v>1.594692862154749</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1187654354996731</v>
+        <v>0.1190579245609942</v>
       </c>
       <c r="C48">
-        <v>12.15446268634699</v>
+        <v>11.75237024020721</v>
       </c>
       <c r="D48">
-        <v>24.45730268634698</v>
+        <v>24.36875024020721</v>
       </c>
       <c r="E48">
-        <v>13.76884</v>
+        <v>14.08238</v>
       </c>
       <c r="F48">
-        <v>14.42284</v>
+        <v>14.73638</v>
       </c>
       <c r="G48">
         <v>2.12</v>
@@ -5223,28 +5223,28 @@
         <v>2.07</v>
       </c>
       <c r="M48">
-        <v>1.2980556</v>
+        <v>1.3262742</v>
       </c>
       <c r="N48">
-        <v>0.7719444000000002</v>
+        <v>0.7437258000000002</v>
       </c>
       <c r="O48">
-        <v>0.07719444000000003</v>
+        <v>0.07437258000000002</v>
       </c>
       <c r="P48">
-        <v>0.6947499600000002</v>
+        <v>0.6693532200000002</v>
       </c>
       <c r="Q48">
-        <v>1.32474996</v>
+        <v>1.29935322</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1509359916660613</v>
+        <v>0.1528074048320645</v>
       </c>
       <c r="T48">
-        <v>1.626420353821837</v>
+        <v>1.6553705203192</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.594692862154749</v>
+        <v>1.560763226789754</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1190579245609942</v>
+        <v>0.1193504136223153</v>
       </c>
       <c r="C49">
-        <v>11.75237024020721</v>
+        <v>11.35091672358731</v>
       </c>
       <c r="D49">
-        <v>24.36875024020721</v>
+        <v>24.28083672358731</v>
       </c>
       <c r="E49">
-        <v>14.08238</v>
+        <v>14.39592</v>
       </c>
       <c r="F49">
-        <v>14.73638</v>
+        <v>15.04992</v>
       </c>
       <c r="G49">
         <v>2.12</v>
@@ -5305,28 +5305,28 @@
         <v>2.07</v>
       </c>
       <c r="M49">
-        <v>1.3262742</v>
+        <v>1.3544928</v>
       </c>
       <c r="N49">
-        <v>0.7437258000000002</v>
+        <v>0.7155072000000002</v>
       </c>
       <c r="O49">
-        <v>0.07437258000000002</v>
+        <v>0.07155072000000003</v>
       </c>
       <c r="P49">
-        <v>0.6693532200000002</v>
+        <v>0.6439564800000002</v>
       </c>
       <c r="Q49">
-        <v>1.29935322</v>
+        <v>1.27395648</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1528074048320645</v>
+        <v>0.1547507954275294</v>
       </c>
       <c r="T49">
-        <v>1.6553705203192</v>
+        <v>1.685434154758769</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.560763226789754</v>
+        <v>1.528247326231635</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1193504136223153</v>
+        <v>0.1455225280074846</v>
       </c>
       <c r="C50">
-        <v>11.35091672358732</v>
+        <v>5.11199089978513</v>
       </c>
       <c r="D50">
-        <v>24.28083672358732</v>
+        <v>18.35545089978513</v>
       </c>
       <c r="E50">
-        <v>14.39592</v>
+        <v>14.70946</v>
       </c>
       <c r="F50">
-        <v>15.04992</v>
+        <v>15.36346</v>
       </c>
       <c r="G50">
         <v>2.12</v>
@@ -5387,45 +5387,45 @@
         <v>2.07</v>
       </c>
       <c r="M50">
-        <v>1.3544928</v>
+        <v>2.255355928</v>
       </c>
       <c r="N50">
-        <v>0.7155072000000005</v>
+        <v>-0.1853559279999999</v>
       </c>
       <c r="O50">
-        <v>0.07155072000000005</v>
+        <v>-0.01853559279999999</v>
       </c>
       <c r="P50">
-        <v>0.6439564800000004</v>
+        <v>-0.1668203351999999</v>
       </c>
       <c r="Q50">
-        <v>1.27395648</v>
+        <v>0.4631796648000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1547507954275294</v>
+        <v>0.1572403067780495</v>
       </c>
       <c r="T50">
-        <v>1.685434154758768</v>
+        <v>1.723946103591829</v>
       </c>
       <c r="U50">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1</v>
+        <v>0.0917815221225694</v>
       </c>
       <c r="W50">
-        <v>0.081</v>
+        <v>0.1333264725524068</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y50">
-        <v>1.528247326231635</v>
+        <v>0.9178152212256939</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1455225280074846</v>
+        <v>0.1465325280074846</v>
       </c>
       <c r="C51">
-        <v>5.11199089978513</v>
+        <v>4.627201216077488</v>
       </c>
       <c r="D51">
-        <v>18.35545089978513</v>
+        <v>18.18420121607749</v>
       </c>
       <c r="E51">
-        <v>14.70946</v>
+        <v>15.023</v>
       </c>
       <c r="F51">
-        <v>15.36346</v>
+        <v>15.677</v>
       </c>
       <c r="G51">
         <v>2.12</v>
@@ -5469,37 +5469,37 @@
         <v>2.07</v>
       </c>
       <c r="M51">
-        <v>2.255355928</v>
+        <v>2.3013836</v>
       </c>
       <c r="N51">
-        <v>-0.1853559279999999</v>
+        <v>-0.2313836</v>
       </c>
       <c r="O51">
-        <v>-0.01853559279999999</v>
+        <v>-0.02313836</v>
       </c>
       <c r="P51">
-        <v>-0.1668203351999999</v>
+        <v>-0.20824524</v>
       </c>
       <c r="Q51">
-        <v>0.4631796648000001</v>
+        <v>0.42175476</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1572403067780495</v>
+        <v>0.1594691129136105</v>
       </c>
       <c r="T51">
-        <v>1.723946103591829</v>
+        <v>1.758425025663665</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.0917815221225694</v>
+        <v>0.089945891680118</v>
       </c>
       <c r="W51">
-        <v>0.1333264725524068</v>
+        <v>0.1335959431013587</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.9178152212256939</v>
+        <v>0.89945891680118</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1465325280074846</v>
+        <v>0.1475425280074846</v>
       </c>
       <c r="C52">
-        <v>4.627201216077488</v>
+        <v>4.145577390644263</v>
       </c>
       <c r="D52">
-        <v>18.18420121607749</v>
+        <v>18.01611739064426</v>
       </c>
       <c r="E52">
-        <v>15.023</v>
+        <v>15.33654</v>
       </c>
       <c r="F52">
-        <v>15.677</v>
+        <v>15.99054</v>
       </c>
       <c r="G52">
         <v>2.12</v>
@@ -5551,37 +5551,37 @@
         <v>2.07</v>
       </c>
       <c r="M52">
-        <v>2.3013836</v>
+        <v>2.347411272</v>
       </c>
       <c r="N52">
-        <v>-0.2313836</v>
+        <v>-0.2774112719999997</v>
       </c>
       <c r="O52">
-        <v>-0.02313836</v>
+        <v>-0.02774112719999997</v>
       </c>
       <c r="P52">
-        <v>-0.20824524</v>
+        <v>-0.2496701447999997</v>
       </c>
       <c r="Q52">
-        <v>0.42175476</v>
+        <v>0.3803298552000003</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1594691129136105</v>
+        <v>0.161788890728174</v>
       </c>
       <c r="T52">
-        <v>1.758425025663665</v>
+        <v>1.794311250677209</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.089945891680118</v>
+        <v>0.08818224674521374</v>
       </c>
       <c r="W52">
-        <v>0.1335959431013587</v>
+        <v>0.1338548461778026</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.89945891680118</v>
+        <v>0.8818224674521373</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1475425280074846</v>
+        <v>0.1485525280074846</v>
       </c>
       <c r="C53">
-        <v>4.145577390644263</v>
+        <v>3.667032437657529</v>
       </c>
       <c r="D53">
-        <v>18.01611739064426</v>
+        <v>17.85111243765753</v>
       </c>
       <c r="E53">
-        <v>15.33654</v>
+        <v>15.65008</v>
       </c>
       <c r="F53">
-        <v>15.99054</v>
+        <v>16.30408</v>
       </c>
       <c r="G53">
         <v>2.12</v>
@@ -5633,37 +5633,37 @@
         <v>2.07</v>
       </c>
       <c r="M53">
-        <v>2.347411272</v>
+        <v>2.393438944</v>
       </c>
       <c r="N53">
-        <v>-0.2774112719999997</v>
+        <v>-0.3234389439999998</v>
       </c>
       <c r="O53">
-        <v>-0.02774112719999997</v>
+        <v>-0.03234389439999998</v>
       </c>
       <c r="P53">
-        <v>-0.2496701447999997</v>
+        <v>-0.2910950495999999</v>
       </c>
       <c r="Q53">
-        <v>0.3803298552000003</v>
+        <v>0.3389049504000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.161788890728174</v>
+        <v>0.1642053259516776</v>
       </c>
       <c r="T53">
-        <v>1.794311250677209</v>
+        <v>1.831692735066318</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.08818224674521374</v>
+        <v>0.08648643430780578</v>
       </c>
       <c r="W53">
-        <v>0.1338548461778026</v>
+        <v>0.1341037914436141</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8818224674521373</v>
+        <v>0.8648643430780577</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1485525280074846</v>
+        <v>0.1495625280074846</v>
       </c>
       <c r="C54">
-        <v>3.667032437657529</v>
+        <v>3.191482529090557</v>
       </c>
       <c r="D54">
-        <v>17.85111243765753</v>
+        <v>17.68910252909055</v>
       </c>
       <c r="E54">
-        <v>15.65008</v>
+        <v>15.96362</v>
       </c>
       <c r="F54">
-        <v>16.30408</v>
+        <v>16.61762</v>
       </c>
       <c r="G54">
         <v>2.12</v>
@@ -5715,37 +5715,37 @@
         <v>2.07</v>
       </c>
       <c r="M54">
-        <v>2.393438944</v>
+        <v>2.439466616</v>
       </c>
       <c r="N54">
-        <v>-0.3234389439999998</v>
+        <v>-0.369466616</v>
       </c>
       <c r="O54">
-        <v>-0.03234389439999998</v>
+        <v>-0.0369466616</v>
       </c>
       <c r="P54">
-        <v>-0.2910950495999999</v>
+        <v>-0.3325199544</v>
       </c>
       <c r="Q54">
-        <v>0.3389049504000001</v>
+        <v>0.2974800456</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1642053259516776</v>
+        <v>0.1667245882059686</v>
       </c>
       <c r="T54">
-        <v>1.831692735066318</v>
+        <v>1.870664920918793</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.08648643430780578</v>
+        <v>0.08485461479256416</v>
       </c>
       <c r="W54">
-        <v>0.1341037914436141</v>
+        <v>0.1343433425484516</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8648643430780577</v>
+        <v>0.8485461479256415</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1495625280074846</v>
+        <v>0.1505725280074846</v>
       </c>
       <c r="C55">
-        <v>3.191482529090557</v>
+        <v>2.718846852711586</v>
       </c>
       <c r="D55">
-        <v>17.68910252909055</v>
+        <v>17.53000685271159</v>
       </c>
       <c r="E55">
-        <v>15.96362</v>
+        <v>16.27716</v>
       </c>
       <c r="F55">
-        <v>16.61762</v>
+        <v>16.93116</v>
       </c>
       <c r="G55">
         <v>2.12</v>
@@ -5797,37 +5797,37 @@
         <v>2.07</v>
       </c>
       <c r="M55">
-        <v>2.439466616</v>
+        <v>2.485494288</v>
       </c>
       <c r="N55">
-        <v>-0.369466616</v>
+        <v>-0.4154942880000001</v>
       </c>
       <c r="O55">
-        <v>-0.0369466616</v>
+        <v>-0.04154942880000001</v>
       </c>
       <c r="P55">
-        <v>-0.3325199544</v>
+        <v>-0.3739448592000001</v>
       </c>
       <c r="Q55">
-        <v>0.2974800456</v>
+        <v>0.2560551407999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1667245882059686</v>
+        <v>0.1693533836017505</v>
       </c>
       <c r="T55">
-        <v>1.870664920918793</v>
+        <v>1.911331549634419</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.08485461479256416</v>
+        <v>0.0832832330371463</v>
       </c>
       <c r="W55">
-        <v>0.1343433425484516</v>
+        <v>0.1345740213901469</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8485461479256415</v>
+        <v>0.8328323303714629</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1505725280074846</v>
+        <v>0.1515825280074846</v>
       </c>
       <c r="C56">
-        <v>2.718846852711586</v>
+        <v>2.249047477672516</v>
       </c>
       <c r="D56">
-        <v>17.53000685271159</v>
+        <v>17.37374747767252</v>
       </c>
       <c r="E56">
-        <v>16.27716</v>
+        <v>16.5907</v>
       </c>
       <c r="F56">
-        <v>16.93116</v>
+        <v>17.2447</v>
       </c>
       <c r="G56">
         <v>2.12</v>
@@ -5879,37 +5879,37 @@
         <v>2.07</v>
       </c>
       <c r="M56">
-        <v>2.485494288</v>
+        <v>2.531521960000001</v>
       </c>
       <c r="N56">
-        <v>-0.4154942880000001</v>
+        <v>-0.4615219600000002</v>
       </c>
       <c r="O56">
-        <v>-0.04154942880000001</v>
+        <v>-0.04615219600000003</v>
       </c>
       <c r="P56">
-        <v>-0.3739448592000001</v>
+        <v>-0.4153697640000002</v>
       </c>
       <c r="Q56">
-        <v>0.2560551407999999</v>
+        <v>0.2146302359999998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1693533836017505</v>
+        <v>0.1720990143484561</v>
       </c>
       <c r="T56">
-        <v>1.911331549634419</v>
+        <v>1.95380558407074</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.0832832330371463</v>
+        <v>0.0817689924364709</v>
       </c>
       <c r="W56">
-        <v>0.1345740213901469</v>
+        <v>0.1347963119103261</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8328323303714629</v>
+        <v>0.817689924364709</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1515825280074846</v>
+        <v>0.1525925280074846</v>
       </c>
       <c r="C57">
-        <v>2.249047477672516</v>
+        <v>1.782009227222801</v>
       </c>
       <c r="D57">
-        <v>17.37374747767252</v>
+        <v>17.2202492272228</v>
       </c>
       <c r="E57">
-        <v>16.5907</v>
+        <v>16.90424</v>
       </c>
       <c r="F57">
-        <v>17.2447</v>
+        <v>17.55824</v>
       </c>
       <c r="G57">
         <v>2.12</v>
@@ -5961,37 +5961,37 @@
         <v>2.07</v>
       </c>
       <c r="M57">
-        <v>2.531521960000001</v>
+        <v>2.577549632000001</v>
       </c>
       <c r="N57">
-        <v>-0.4615219600000002</v>
+        <v>-0.5075496320000004</v>
       </c>
       <c r="O57">
-        <v>-0.04615219600000003</v>
+        <v>-0.05075496320000004</v>
       </c>
       <c r="P57">
-        <v>-0.4153697640000002</v>
+        <v>-0.4567946688000003</v>
       </c>
       <c r="Q57">
-        <v>0.2146302359999998</v>
+        <v>0.1732053311999997</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1720990143484561</v>
+        <v>0.1749694464927392</v>
       </c>
       <c r="T57">
-        <v>1.95380558407074</v>
+        <v>1.998210256435983</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.0817689924364709</v>
+        <v>0.0803088318572482</v>
       </c>
       <c r="W57">
-        <v>0.1347963119103261</v>
+        <v>0.135010663483356</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.817689924364709</v>
+        <v>0.803088318572482</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1525925280074846</v>
+        <v>0.1851022722305586</v>
       </c>
       <c r="C58">
-        <v>1.782009227222801</v>
+        <v>-2.344359753534803</v>
       </c>
       <c r="D58">
-        <v>17.2202492272228</v>
+        <v>13.4074202464652</v>
       </c>
       <c r="E58">
-        <v>16.90424</v>
+        <v>17.21778</v>
       </c>
       <c r="F58">
-        <v>17.55824</v>
+        <v>17.87178</v>
       </c>
       <c r="G58">
         <v>2.12</v>
@@ -6043,45 +6043,45 @@
         <v>2.07</v>
       </c>
       <c r="M58">
-        <v>2.577549632000001</v>
+        <v>3.588653424</v>
       </c>
       <c r="N58">
-        <v>-0.5075496320000004</v>
+        <v>-1.518653424</v>
       </c>
       <c r="O58">
-        <v>-0.05075496320000004</v>
+        <v>-0.1518653424</v>
       </c>
       <c r="P58">
-        <v>-0.4567946688000003</v>
+        <v>-1.3667880816</v>
       </c>
       <c r="Q58">
-        <v>0.1732053311999997</v>
+        <v>-0.7367880816</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1749694464927392</v>
+        <v>0.1796472108834401</v>
       </c>
       <c r="T58">
-        <v>1.998210256435983</v>
+        <v>2.070573783852779</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.0803088318572482</v>
+        <v>0.05768180304501871</v>
       </c>
       <c r="W58">
-        <v>0.135010663483356</v>
+        <v>0.1892174939485602</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.803088318572482</v>
+        <v>0.5768180304501871</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1851022722305586</v>
+        <v>0.1866522722305586</v>
       </c>
       <c r="C59">
-        <v>-2.344359753534803</v>
+        <v>-2.797958616962525</v>
       </c>
       <c r="D59">
-        <v>13.4074202464652</v>
+        <v>13.26736138303748</v>
       </c>
       <c r="E59">
-        <v>17.21778</v>
+        <v>17.53132</v>
       </c>
       <c r="F59">
-        <v>17.87178</v>
+        <v>18.18532</v>
       </c>
       <c r="G59">
         <v>2.12</v>
@@ -6125,37 +6125,37 @@
         <v>2.07</v>
       </c>
       <c r="M59">
-        <v>3.588653424</v>
+        <v>3.651612256</v>
       </c>
       <c r="N59">
-        <v>-1.518653424</v>
+        <v>-1.581612256</v>
       </c>
       <c r="O59">
-        <v>-0.1518653424</v>
+        <v>-0.1581612256</v>
       </c>
       <c r="P59">
-        <v>-1.3667880816</v>
+        <v>-1.4234510304</v>
       </c>
       <c r="Q59">
-        <v>-0.7367880816</v>
+        <v>-0.7934510304000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1796472108834401</v>
+        <v>0.1828340492378077</v>
       </c>
       <c r="T59">
-        <v>2.070573783852779</v>
+        <v>2.119873159658797</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.05768180304501871</v>
+        <v>0.05668728919941494</v>
       </c>
       <c r="W59">
-        <v>0.1892174939485602</v>
+        <v>0.1894171923287575</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5768180304501871</v>
+        <v>0.5668728919941494</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1866522722305586</v>
+        <v>0.1882022722305586</v>
       </c>
       <c r="C60">
-        <v>-2.797958616962514</v>
+        <v>-3.248661519441992</v>
       </c>
       <c r="D60">
-        <v>13.26736138303748</v>
+        <v>13.130198480558</v>
       </c>
       <c r="E60">
-        <v>17.53132</v>
+        <v>17.84486</v>
       </c>
       <c r="F60">
-        <v>18.18532</v>
+        <v>18.49886</v>
       </c>
       <c r="G60">
         <v>2.12</v>
@@ -6207,37 +6207,37 @@
         <v>2.07</v>
       </c>
       <c r="M60">
-        <v>3.651612256</v>
+        <v>3.714571088</v>
       </c>
       <c r="N60">
-        <v>-1.581612255999999</v>
+        <v>-1.644571087999999</v>
       </c>
       <c r="O60">
-        <v>-0.1581612255999999</v>
+        <v>-0.1644571087999999</v>
       </c>
       <c r="P60">
-        <v>-1.423451030399999</v>
+        <v>-1.480113979199999</v>
       </c>
       <c r="Q60">
-        <v>-0.7934510303999992</v>
+        <v>-0.8501139791999993</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1828340492378077</v>
+        <v>0.1861763431216567</v>
       </c>
       <c r="T60">
-        <v>2.119873159658796</v>
+        <v>2.171577383065109</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.05668728919941495</v>
+        <v>0.05572648768756046</v>
       </c>
       <c r="W60">
-        <v>0.1894171923287575</v>
+        <v>0.1896101212723379</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5668728919941495</v>
+        <v>0.5572648768756046</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1882022722305586</v>
+        <v>0.1897522722305586</v>
       </c>
       <c r="C61">
-        <v>-3.248661519441992</v>
+        <v>-3.696557360452395</v>
       </c>
       <c r="D61">
-        <v>13.130198480558</v>
+        <v>12.9958426395476</v>
       </c>
       <c r="E61">
-        <v>17.84486</v>
+        <v>18.1584</v>
       </c>
       <c r="F61">
-        <v>18.49886</v>
+        <v>18.8124</v>
       </c>
       <c r="G61">
         <v>2.12</v>
@@ -6289,37 +6289,37 @@
         <v>2.07</v>
       </c>
       <c r="M61">
-        <v>3.714571088</v>
+        <v>3.77752992</v>
       </c>
       <c r="N61">
-        <v>-1.644571087999999</v>
+        <v>-1.70752992</v>
       </c>
       <c r="O61">
-        <v>-0.1644571087999999</v>
+        <v>-0.170752992</v>
       </c>
       <c r="P61">
-        <v>-1.480113979199999</v>
+        <v>-1.536776928</v>
       </c>
       <c r="Q61">
-        <v>-0.8501139791999993</v>
+        <v>-0.9067769279999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1861763431216567</v>
+        <v>0.1896857516996981</v>
       </c>
       <c r="T61">
-        <v>2.171577383065109</v>
+        <v>2.225866817641736</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.05572648768756046</v>
+        <v>0.05479771289276778</v>
       </c>
       <c r="W61">
-        <v>0.1896101212723379</v>
+        <v>0.1897966192511322</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5572648768756046</v>
+        <v>0.5479771289276778</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1897522722305586</v>
+        <v>0.1913022722305586</v>
       </c>
       <c r="C62">
-        <v>-3.696557360452395</v>
+        <v>-4.141731437643834</v>
       </c>
       <c r="D62">
-        <v>12.9958426395476</v>
+        <v>12.86420856235617</v>
       </c>
       <c r="E62">
-        <v>18.1584</v>
+        <v>18.47194</v>
       </c>
       <c r="F62">
-        <v>18.8124</v>
+        <v>19.12594</v>
       </c>
       <c r="G62">
         <v>2.12</v>
@@ -6371,37 +6371,37 @@
         <v>2.07</v>
       </c>
       <c r="M62">
-        <v>3.77752992</v>
+        <v>3.840488752</v>
       </c>
       <c r="N62">
-        <v>-1.70752992</v>
+        <v>-1.770488752</v>
       </c>
       <c r="O62">
-        <v>-0.170752992</v>
+        <v>-0.1770488752</v>
       </c>
       <c r="P62">
-        <v>-1.536776928</v>
+        <v>-1.5934398768</v>
       </c>
       <c r="Q62">
-        <v>-0.9067769279999999</v>
+        <v>-0.9634398767999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1896857516996981</v>
+        <v>0.1933751299484083</v>
       </c>
       <c r="T62">
-        <v>2.225866817641736</v>
+        <v>2.282940325786396</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.05479771289276778</v>
+        <v>0.05389938973059125</v>
       </c>
       <c r="W62">
-        <v>0.1897966192511322</v>
+        <v>0.1899770025420973</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5479771289276778</v>
+        <v>0.5389938973059125</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1913022722305586</v>
+        <v>0.1928522722305586</v>
       </c>
       <c r="C63">
-        <v>-4.141731437643834</v>
+        <v>-4.584265627421715</v>
       </c>
       <c r="D63">
-        <v>12.86420856235617</v>
+        <v>12.73521437257829</v>
       </c>
       <c r="E63">
-        <v>18.47194</v>
+        <v>18.78548</v>
       </c>
       <c r="F63">
-        <v>19.12594</v>
+        <v>19.43948</v>
       </c>
       <c r="G63">
         <v>2.12</v>
@@ -6453,37 +6453,37 @@
         <v>2.07</v>
       </c>
       <c r="M63">
-        <v>3.840488752</v>
+        <v>3.903447584</v>
       </c>
       <c r="N63">
-        <v>-1.770488752</v>
+        <v>-1.833447584</v>
       </c>
       <c r="O63">
-        <v>-0.1770488752</v>
+        <v>-0.1833447584</v>
       </c>
       <c r="P63">
-        <v>-1.5934398768</v>
+        <v>-1.6501028256</v>
       </c>
       <c r="Q63">
-        <v>-0.9634398767999998</v>
+        <v>-1.0201028256</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1933751299484083</v>
+        <v>0.1972586859996822</v>
       </c>
       <c r="T63">
-        <v>2.282940325786396</v>
+        <v>2.343017702780775</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.05389938973059125</v>
+        <v>0.05303004473493655</v>
       </c>
       <c r="W63">
-        <v>0.1899770025420973</v>
+        <v>0.1901515670172247</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5389938973059125</v>
+        <v>0.5303004473493655</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1928522722305586</v>
+        <v>0.1944022722305586</v>
       </c>
       <c r="C64">
-        <v>-4.584265627421715</v>
+        <v>-5.024238554774339</v>
       </c>
       <c r="D64">
-        <v>12.73521437257829</v>
+        <v>12.60878144522566</v>
       </c>
       <c r="E64">
-        <v>18.78548</v>
+        <v>19.09902</v>
       </c>
       <c r="F64">
-        <v>19.43948</v>
+        <v>19.75302</v>
       </c>
       <c r="G64">
         <v>2.12</v>
@@ -6535,37 +6535,37 @@
         <v>2.07</v>
       </c>
       <c r="M64">
-        <v>3.903447584</v>
+        <v>3.966406416</v>
       </c>
       <c r="N64">
-        <v>-1.833447584</v>
+        <v>-1.896406416</v>
       </c>
       <c r="O64">
-        <v>-0.1833447584</v>
+        <v>-0.1896406416</v>
       </c>
       <c r="P64">
-        <v>-1.6501028256</v>
+        <v>-1.7067657744</v>
       </c>
       <c r="Q64">
-        <v>-1.0201028256</v>
+        <v>-1.0767657744</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1972586859996822</v>
+        <v>0.2013521639996736</v>
       </c>
       <c r="T64">
-        <v>2.343017702780775</v>
+        <v>2.406342505558634</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.05303004473493655</v>
+        <v>0.05218829799311217</v>
       </c>
       <c r="W64">
-        <v>0.1901515670172247</v>
+        <v>0.1903205897629831</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5303004473493655</v>
+        <v>0.5218829799311218</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1944022722305586</v>
+        <v>0.1959522722305586</v>
       </c>
       <c r="C65">
-        <v>-5.024238554774339</v>
+        <v>-5.461725753083677</v>
       </c>
       <c r="D65">
-        <v>12.60878144522566</v>
+        <v>12.48483424691632</v>
       </c>
       <c r="E65">
-        <v>19.09902</v>
+        <v>19.41256</v>
       </c>
       <c r="F65">
-        <v>19.75302</v>
+        <v>20.06656</v>
       </c>
       <c r="G65">
         <v>2.12</v>
@@ -6617,37 +6617,37 @@
         <v>2.07</v>
       </c>
       <c r="M65">
-        <v>3.966406416</v>
+        <v>4.029365248</v>
       </c>
       <c r="N65">
-        <v>-1.896406416</v>
+        <v>-1.959365247999999</v>
       </c>
       <c r="O65">
-        <v>-0.1896406416</v>
+        <v>-0.1959365247999999</v>
       </c>
       <c r="P65">
-        <v>-1.7067657744</v>
+        <v>-1.763428723199999</v>
       </c>
       <c r="Q65">
-        <v>-1.0767657744</v>
+        <v>-1.133428723199999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2013521639996736</v>
+        <v>0.205673057444109</v>
       </c>
       <c r="T65">
-        <v>2.406342505558634</v>
+        <v>2.473185352935263</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.05218829799311217</v>
+        <v>0.0513728558369698</v>
       </c>
       <c r="W65">
-        <v>0.1903205897629831</v>
+        <v>0.1904843305479365</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5218829799311218</v>
+        <v>0.513728558369698</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1959522722305586</v>
+        <v>0.1975022722305586</v>
       </c>
       <c r="C66">
-        <v>-5.461725753083677</v>
+        <v>-5.896799814602179</v>
       </c>
       <c r="D66">
-        <v>12.48483424691632</v>
+        <v>12.36330018539782</v>
       </c>
       <c r="E66">
-        <v>19.41256</v>
+        <v>19.7261</v>
       </c>
       <c r="F66">
-        <v>20.06656</v>
+        <v>20.3801</v>
       </c>
       <c r="G66">
         <v>2.12</v>
@@ -6699,37 +6699,37 @@
         <v>2.07</v>
       </c>
       <c r="M66">
-        <v>4.029365248</v>
+        <v>4.09232408</v>
       </c>
       <c r="N66">
-        <v>-1.959365247999999</v>
+        <v>-2.02232408</v>
       </c>
       <c r="O66">
-        <v>-0.1959365247999999</v>
+        <v>-0.202232408</v>
       </c>
       <c r="P66">
-        <v>-1.763428723199999</v>
+        <v>-1.820091672</v>
       </c>
       <c r="Q66">
-        <v>-1.133428723199999</v>
+        <v>-1.190091672</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.205673057444109</v>
+        <v>0.2102408590853693</v>
       </c>
       <c r="T66">
-        <v>2.473185352935263</v>
+        <v>2.543847791590557</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.0513728558369698</v>
+        <v>0.05058250420870872</v>
       </c>
       <c r="W66">
-        <v>0.1904843305479365</v>
+        <v>0.1906430331548913</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.513728558369698</v>
+        <v>0.5058250420870871</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1975022722305586</v>
+        <v>0.2224426977181151</v>
       </c>
       <c r="C67">
-        <v>-5.896799814602179</v>
+        <v>-7.884610477943461</v>
       </c>
       <c r="D67">
-        <v>12.36330018539782</v>
+        <v>10.68902952205654</v>
       </c>
       <c r="E67">
-        <v>19.7261</v>
+        <v>20.03964</v>
       </c>
       <c r="F67">
-        <v>20.3801</v>
+        <v>20.69364</v>
       </c>
       <c r="G67">
         <v>2.12</v>
@@ -6781,45 +6781,45 @@
         <v>2.07</v>
       </c>
       <c r="M67">
-        <v>4.09232408</v>
+        <v>4.879560312000001</v>
       </c>
       <c r="N67">
-        <v>-2.02232408</v>
+        <v>-2.809560312</v>
       </c>
       <c r="O67">
-        <v>-0.202232408</v>
+        <v>-0.2809560312000001</v>
       </c>
       <c r="P67">
-        <v>-1.820091672</v>
+        <v>-2.5286042808</v>
       </c>
       <c r="Q67">
-        <v>-1.190091672</v>
+        <v>-1.8986042808</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2102408590853693</v>
+        <v>0.2159315475512815</v>
       </c>
       <c r="T67">
-        <v>2.543847791590557</v>
+        <v>2.631880932302412</v>
       </c>
       <c r="U67">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05058250420870872</v>
+        <v>0.04242185499602039</v>
       </c>
       <c r="W67">
-        <v>0.1906430331548913</v>
+        <v>0.2257969265919384</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y67">
-        <v>0.5058250420870871</v>
+        <v>0.4242185499602039</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2224426977181151</v>
+        <v>0.2243426977181151</v>
       </c>
       <c r="C68">
-        <v>-7.884610477943461</v>
+        <v>-8.307299974990123</v>
       </c>
       <c r="D68">
-        <v>10.68902952205654</v>
+        <v>10.57988002500988</v>
       </c>
       <c r="E68">
-        <v>20.03964</v>
+        <v>20.35318</v>
       </c>
       <c r="F68">
-        <v>20.69364</v>
+        <v>21.00718</v>
       </c>
       <c r="G68">
         <v>2.12</v>
@@ -6863,37 +6863,37 @@
         <v>2.07</v>
       </c>
       <c r="M68">
-        <v>4.879560312000001</v>
+        <v>4.953493044000001</v>
       </c>
       <c r="N68">
-        <v>-2.809560312</v>
+        <v>-2.883493044000001</v>
       </c>
       <c r="O68">
-        <v>-0.2809560312000001</v>
+        <v>-0.2883493044000001</v>
       </c>
       <c r="P68">
-        <v>-2.5286042808</v>
+        <v>-2.595143739600001</v>
       </c>
       <c r="Q68">
-        <v>-1.8986042808</v>
+        <v>-1.965143739600001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2159315475512815</v>
+        <v>0.2210870489922295</v>
       </c>
       <c r="T68">
-        <v>2.631880932302412</v>
+        <v>2.71163489994794</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04242185499602039</v>
+        <v>0.04178869298115441</v>
       </c>
       <c r="W68">
-        <v>0.2257969265919384</v>
+        <v>0.2259462261950438</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.4242185499602039</v>
+        <v>0.4178869298115441</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2243426977181151</v>
+        <v>0.2262426977181151</v>
       </c>
       <c r="C69">
-        <v>-8.307299974990123</v>
+        <v>-8.727782875408884</v>
       </c>
       <c r="D69">
-        <v>10.57988002500988</v>
+        <v>10.47293712459112</v>
       </c>
       <c r="E69">
-        <v>20.35318</v>
+        <v>20.66672</v>
       </c>
       <c r="F69">
-        <v>21.00718</v>
+        <v>21.32072</v>
       </c>
       <c r="G69">
         <v>2.12</v>
@@ -6945,37 +6945,37 @@
         <v>2.07</v>
       </c>
       <c r="M69">
-        <v>4.953493044000001</v>
+        <v>5.027425776</v>
       </c>
       <c r="N69">
-        <v>-2.883493044000001</v>
+        <v>-2.957425776</v>
       </c>
       <c r="O69">
-        <v>-0.2883493044000001</v>
+        <v>-0.2957425776</v>
       </c>
       <c r="P69">
-        <v>-2.595143739600001</v>
+        <v>-2.6616831984</v>
       </c>
       <c r="Q69">
-        <v>-1.965143739600001</v>
+        <v>-2.0316831984</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2210870489922295</v>
+        <v>0.2265647692732367</v>
       </c>
       <c r="T69">
-        <v>2.71163489994794</v>
+        <v>2.796373490571313</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04178869298115441</v>
+        <v>0.04117415337849038</v>
       </c>
       <c r="W69">
-        <v>0.2259462261950438</v>
+        <v>0.226091134633352</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4178869298115441</v>
+        <v>0.4117415337849037</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2262426977181151</v>
+        <v>0.2281426977181151</v>
       </c>
       <c r="C70">
-        <v>-8.727782875408884</v>
+        <v>-9.146125423352487</v>
       </c>
       <c r="D70">
-        <v>10.47293712459112</v>
+        <v>10.36813457664751</v>
       </c>
       <c r="E70">
-        <v>20.66672</v>
+        <v>20.98026</v>
       </c>
       <c r="F70">
-        <v>21.32072</v>
+        <v>21.63426</v>
       </c>
       <c r="G70">
         <v>2.12</v>
@@ -7027,37 +7027,37 @@
         <v>2.07</v>
       </c>
       <c r="M70">
-        <v>5.027425776</v>
+        <v>5.101358508000001</v>
       </c>
       <c r="N70">
-        <v>-2.957425776</v>
+        <v>-3.031358508</v>
       </c>
       <c r="O70">
-        <v>-0.2957425776</v>
+        <v>-0.3031358508000001</v>
       </c>
       <c r="P70">
-        <v>-2.6616831984</v>
+        <v>-2.7282226572</v>
       </c>
       <c r="Q70">
-        <v>-2.0316831984</v>
+        <v>-2.0982226572</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2265647692732367</v>
+        <v>0.2323958908626959</v>
       </c>
       <c r="T70">
-        <v>2.796373490571313</v>
+        <v>2.886579087041356</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04117415337849038</v>
+        <v>0.04057742651793255</v>
       </c>
       <c r="W70">
-        <v>0.226091134633352</v>
+        <v>0.2262318428270715</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.4117415337849037</v>
+        <v>0.4057742651793255</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2281426977181151</v>
+        <v>0.2300426977181151</v>
       </c>
       <c r="C71">
-        <v>-9.146125423352487</v>
+        <v>-9.562391237627942</v>
       </c>
       <c r="D71">
-        <v>10.36813457664751</v>
+        <v>10.26540876237206</v>
       </c>
       <c r="E71">
-        <v>20.98026</v>
+        <v>21.2938</v>
       </c>
       <c r="F71">
-        <v>21.63426</v>
+        <v>21.9478</v>
       </c>
       <c r="G71">
         <v>2.12</v>
@@ -7109,37 +7109,37 @@
         <v>2.07</v>
       </c>
       <c r="M71">
-        <v>5.101358508000001</v>
+        <v>5.175291240000001</v>
       </c>
       <c r="N71">
-        <v>-3.031358508</v>
+        <v>-3.105291240000001</v>
       </c>
       <c r="O71">
-        <v>-0.3031358508000001</v>
+        <v>-0.3105291240000001</v>
       </c>
       <c r="P71">
-        <v>-2.7282226572</v>
+        <v>-2.794762116</v>
       </c>
       <c r="Q71">
-        <v>-2.0982226572</v>
+        <v>-2.164762116</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2323958908626959</v>
+        <v>0.2386157538914524</v>
       </c>
       <c r="T71">
-        <v>2.886579087041356</v>
+        <v>2.982798389942734</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04057742651793255</v>
+        <v>0.0399977489962478</v>
       </c>
       <c r="W71">
-        <v>0.2262318428270715</v>
+        <v>0.2263685307866848</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4057742651793255</v>
+        <v>0.399977489962478</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2300426977181151</v>
+        <v>0.2319426977181151</v>
       </c>
       <c r="C72">
-        <v>-9.562391237627942</v>
+        <v>-9.976641440478048</v>
       </c>
       <c r="D72">
-        <v>10.26540876237206</v>
+        <v>10.16469855952195</v>
       </c>
       <c r="E72">
-        <v>21.2938</v>
+        <v>21.60734</v>
       </c>
       <c r="F72">
-        <v>21.9478</v>
+        <v>22.26134</v>
       </c>
       <c r="G72">
         <v>2.12</v>
@@ -7191,37 +7191,37 @@
         <v>2.07</v>
       </c>
       <c r="M72">
-        <v>5.175291240000001</v>
+        <v>5.249223972</v>
       </c>
       <c r="N72">
-        <v>-3.105291240000001</v>
+        <v>-3.179223972</v>
       </c>
       <c r="O72">
-        <v>-0.3105291240000001</v>
+        <v>-0.3179223972</v>
       </c>
       <c r="P72">
-        <v>-2.794762116</v>
+        <v>-2.8613015748</v>
       </c>
       <c r="Q72">
-        <v>-2.164762116</v>
+        <v>-2.2313015748</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2386157538914524</v>
+        <v>0.2452645729911577</v>
       </c>
       <c r="T72">
-        <v>2.982798389942734</v>
+        <v>3.085653506837311</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.0399977489962478</v>
+        <v>0.03943440041883586</v>
       </c>
       <c r="W72">
-        <v>0.2263685307866848</v>
+        <v>0.2265013683812385</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.399977489962478</v>
+        <v>0.3943440041883586</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.231942697718115</v>
+        <v>0.2338426977181151</v>
       </c>
       <c r="C73">
-        <v>-9.976641440478041</v>
+        <v>-10.38893477885609</v>
       </c>
       <c r="D73">
-        <v>10.16469855952196</v>
+        <v>10.06594522114391</v>
       </c>
       <c r="E73">
-        <v>21.60734</v>
+        <v>21.92088</v>
       </c>
       <c r="F73">
-        <v>22.26134</v>
+        <v>22.57488</v>
       </c>
       <c r="G73">
         <v>2.12</v>
@@ -7273,37 +7273,37 @@
         <v>2.07</v>
       </c>
       <c r="M73">
-        <v>5.249223971999999</v>
+        <v>5.323156704000001</v>
       </c>
       <c r="N73">
-        <v>-3.179223971999999</v>
+        <v>-3.253156704</v>
       </c>
       <c r="O73">
-        <v>-0.3179223971999999</v>
+        <v>-0.3253156704</v>
       </c>
       <c r="P73">
-        <v>-2.861301574799999</v>
+        <v>-2.9278410336</v>
       </c>
       <c r="Q73">
-        <v>-2.231301574799999</v>
+        <v>-2.2978410336</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2452645729911576</v>
+        <v>0.2523883077408419</v>
       </c>
       <c r="T73">
-        <v>3.08565350683731</v>
+        <v>3.195855417795786</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03943440041883586</v>
+        <v>0.03888670041301869</v>
       </c>
       <c r="W73">
-        <v>0.2265013683812385</v>
+        <v>0.2266305160426102</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3943440041883587</v>
+        <v>0.3888670041301869</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2338426977181151</v>
+        <v>0.2357426977181151</v>
       </c>
       <c r="C74">
-        <v>-10.38893477885609</v>
+        <v>-10.79932773869915</v>
       </c>
       <c r="D74">
-        <v>10.06594522114391</v>
+        <v>9.969092261300849</v>
       </c>
       <c r="E74">
-        <v>21.92088</v>
+        <v>22.23442</v>
       </c>
       <c r="F74">
-        <v>22.57488</v>
+        <v>22.88842</v>
       </c>
       <c r="G74">
         <v>2.12</v>
@@ -7355,37 +7355,37 @@
         <v>2.07</v>
       </c>
       <c r="M74">
-        <v>5.323156704000001</v>
+        <v>5.397089436</v>
       </c>
       <c r="N74">
-        <v>-3.253156704</v>
+        <v>-3.327089436</v>
       </c>
       <c r="O74">
-        <v>-0.3253156704</v>
+        <v>-0.3327089436</v>
       </c>
       <c r="P74">
-        <v>-2.9278410336</v>
+        <v>-2.994380492399999</v>
       </c>
       <c r="Q74">
-        <v>-2.2978410336</v>
+        <v>-2.3643804924</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2523883077408419</v>
+        <v>0.2600397265460582</v>
       </c>
       <c r="T74">
-        <v>3.195855417795786</v>
+        <v>3.314220433269703</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03888670041301869</v>
+        <v>0.03835400588681296</v>
       </c>
       <c r="W74">
-        <v>0.2266305160426102</v>
+        <v>0.2267561254118895</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3888670041301869</v>
+        <v>0.3835400588681296</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2357426977181151</v>
+        <v>0.2376426977181151</v>
       </c>
       <c r="C75">
-        <v>-10.79932773869915</v>
+        <v>-11.20787465266719</v>
       </c>
       <c r="D75">
-        <v>9.969092261300849</v>
+        <v>9.874085347332807</v>
       </c>
       <c r="E75">
-        <v>22.23442</v>
+        <v>22.54796</v>
       </c>
       <c r="F75">
-        <v>22.88842</v>
+        <v>23.20196</v>
       </c>
       <c r="G75">
         <v>2.12</v>
@@ -7437,37 +7437,37 @@
         <v>2.07</v>
       </c>
       <c r="M75">
-        <v>5.397089436</v>
+        <v>5.471022168</v>
       </c>
       <c r="N75">
-        <v>-3.327089436</v>
+        <v>-3.401022168</v>
       </c>
       <c r="O75">
-        <v>-0.3327089436</v>
+        <v>-0.3401022168</v>
       </c>
       <c r="P75">
-        <v>-2.994380492399999</v>
+        <v>-3.0609199512</v>
       </c>
       <c r="Q75">
-        <v>-2.3643804924</v>
+        <v>-2.4309199512</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2600397265460582</v>
+        <v>0.2682797160285989</v>
       </c>
       <c r="T75">
-        <v>3.314220433269703</v>
+        <v>3.441690449933923</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03835400588681296</v>
+        <v>0.03783570850996414</v>
       </c>
       <c r="W75">
-        <v>0.2267561254118895</v>
+        <v>0.2268783399333505</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3835400588681296</v>
+        <v>0.3783570850996413</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2376426977181151</v>
+        <v>0.239542697718115</v>
       </c>
       <c r="C76">
-        <v>-11.20787465266719</v>
+        <v>-11.61462780177966</v>
       </c>
       <c r="D76">
-        <v>9.874085347332807</v>
+        <v>9.780872198220337</v>
       </c>
       <c r="E76">
-        <v>22.54796</v>
+        <v>22.8615</v>
       </c>
       <c r="F76">
-        <v>23.20196</v>
+        <v>23.5155</v>
       </c>
       <c r="G76">
         <v>2.12</v>
@@ -7519,37 +7519,37 @@
         <v>2.07</v>
       </c>
       <c r="M76">
-        <v>5.471022168</v>
+        <v>5.5449549</v>
       </c>
       <c r="N76">
-        <v>-3.401022168</v>
+        <v>-3.4749549</v>
       </c>
       <c r="O76">
-        <v>-0.3401022168</v>
+        <v>-0.34749549</v>
       </c>
       <c r="P76">
-        <v>-3.0609199512</v>
+        <v>-3.12745941</v>
       </c>
       <c r="Q76">
-        <v>-2.4309199512</v>
+        <v>-2.49745941</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2682797160285989</v>
+        <v>0.2771789046697429</v>
       </c>
       <c r="T76">
-        <v>3.441690449933923</v>
+        <v>3.57935806793128</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03783570850996414</v>
+        <v>0.03733123239649794</v>
       </c>
       <c r="W76">
-        <v>0.2268783399333505</v>
+        <v>0.2269972954009058</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3783570850996413</v>
+        <v>0.3733123239649794</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.239542697718115</v>
+        <v>0.2414426977181151</v>
       </c>
       <c r="C77">
-        <v>-11.61462780177966</v>
+        <v>-12.01963751134921</v>
       </c>
       <c r="D77">
-        <v>9.780872198220337</v>
+        <v>9.689402488650794</v>
       </c>
       <c r="E77">
-        <v>22.8615</v>
+        <v>23.17504</v>
       </c>
       <c r="F77">
-        <v>23.5155</v>
+        <v>23.82904</v>
       </c>
       <c r="G77">
         <v>2.12</v>
@@ -7601,37 +7601,37 @@
         <v>2.07</v>
       </c>
       <c r="M77">
-        <v>5.5449549</v>
+        <v>5.618887632</v>
       </c>
       <c r="N77">
-        <v>-3.4749549</v>
+        <v>-3.548887632</v>
       </c>
       <c r="O77">
-        <v>-0.34749549</v>
+        <v>-0.3548887632</v>
       </c>
       <c r="P77">
-        <v>-3.12745941</v>
+        <v>-3.1939988688</v>
       </c>
       <c r="Q77">
-        <v>-2.49745941</v>
+        <v>-2.5639988688</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2771789046697429</v>
+        <v>0.2868196923643155</v>
       </c>
       <c r="T77">
-        <v>3.57935806793128</v>
+        <v>3.728497987428416</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03733123239649794</v>
+        <v>0.03684003197022824</v>
       </c>
       <c r="W77">
-        <v>0.2269972954009058</v>
+        <v>0.2271131204614202</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3733123239649794</v>
+        <v>0.3684003197022824</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2414426977181151</v>
+        <v>0.2433426977181151</v>
       </c>
       <c r="C78">
-        <v>-12.01963751134921</v>
+        <v>-12.42295224158216</v>
       </c>
       <c r="D78">
-        <v>9.689402488650794</v>
+        <v>9.599627758417835</v>
       </c>
       <c r="E78">
-        <v>23.17504</v>
+        <v>23.48858</v>
       </c>
       <c r="F78">
-        <v>23.82904</v>
+        <v>24.14258</v>
       </c>
       <c r="G78">
         <v>2.12</v>
@@ -7683,37 +7683,37 @@
         <v>2.07</v>
       </c>
       <c r="M78">
-        <v>5.618887632</v>
+        <v>5.692820364</v>
       </c>
       <c r="N78">
-        <v>-3.548887632</v>
+        <v>-3.622820364</v>
       </c>
       <c r="O78">
-        <v>-0.3548887632</v>
+        <v>-0.3622820364</v>
       </c>
       <c r="P78">
-        <v>-3.1939988688</v>
+        <v>-3.2605383276</v>
       </c>
       <c r="Q78">
-        <v>-2.5639988688</v>
+        <v>-2.6305383276</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2868196923643155</v>
+        <v>0.2972988094236336</v>
       </c>
       <c r="T78">
-        <v>3.728497987428416</v>
+        <v>3.890606595577479</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03684003197022824</v>
+        <v>0.03636158999658891</v>
       </c>
       <c r="W78">
-        <v>0.2271131204614202</v>
+        <v>0.2272259370788043</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3684003197022824</v>
+        <v>0.3636158999658891</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2433426977181151</v>
+        <v>0.245242697718115</v>
       </c>
       <c r="C79">
-        <v>-12.42295224158216</v>
+        <v>-12.82461867318876</v>
       </c>
       <c r="D79">
-        <v>9.599627758417835</v>
+        <v>9.511501326811244</v>
       </c>
       <c r="E79">
-        <v>23.48858</v>
+        <v>23.80212</v>
       </c>
       <c r="F79">
-        <v>24.14258</v>
+        <v>24.45612</v>
       </c>
       <c r="G79">
         <v>2.12</v>
@@ -7765,37 +7765,37 @@
         <v>2.07</v>
       </c>
       <c r="M79">
-        <v>5.692820364</v>
+        <v>5.766753096</v>
       </c>
       <c r="N79">
-        <v>-3.622820364</v>
+        <v>-3.696753095999999</v>
       </c>
       <c r="O79">
-        <v>-0.3622820364</v>
+        <v>-0.3696753095999999</v>
       </c>
       <c r="P79">
-        <v>-3.2605383276</v>
+        <v>-3.327077786399999</v>
       </c>
       <c r="Q79">
-        <v>-2.6305383276</v>
+        <v>-2.6970777864</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2972988094236336</v>
+        <v>0.3087305734883442</v>
       </c>
       <c r="T79">
-        <v>3.890606595577479</v>
+        <v>4.06745234992191</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03636158999658891</v>
+        <v>0.03589541576586341</v>
       </c>
       <c r="W79">
-        <v>0.2272259370788043</v>
+        <v>0.2273358609624094</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3636158999658891</v>
+        <v>0.3589541576586341</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.245242697718115</v>
+        <v>0.2471426977181151</v>
       </c>
       <c r="C80">
-        <v>-12.82461867318876</v>
+        <v>-13.22468178832068</v>
       </c>
       <c r="D80">
-        <v>9.511501326811244</v>
+        <v>9.424978211679321</v>
       </c>
       <c r="E80">
-        <v>23.80212</v>
+        <v>24.11566</v>
       </c>
       <c r="F80">
-        <v>24.45612</v>
+        <v>24.76966</v>
       </c>
       <c r="G80">
         <v>2.12</v>
@@ -7847,37 +7847,37 @@
         <v>2.07</v>
       </c>
       <c r="M80">
-        <v>5.766753096</v>
+        <v>5.840685828000001</v>
       </c>
       <c r="N80">
-        <v>-3.696753095999999</v>
+        <v>-3.770685828</v>
       </c>
       <c r="O80">
-        <v>-0.3696753095999999</v>
+        <v>-0.3770685828000001</v>
       </c>
       <c r="P80">
-        <v>-3.327077786399999</v>
+        <v>-3.3936172452</v>
       </c>
       <c r="Q80">
-        <v>-2.6970777864</v>
+        <v>-2.7636172452</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3087305734883442</v>
+        <v>0.3212510769877892</v>
       </c>
       <c r="T80">
-        <v>4.06745234992191</v>
+        <v>4.261140557061048</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03589541576586341</v>
+        <v>0.03544104341439678</v>
       </c>
       <c r="W80">
-        <v>0.2273358609624094</v>
+        <v>0.2274430019628852</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3589541576586341</v>
+        <v>0.3544104341439678</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2471426977181151</v>
+        <v>0.2490426977181151</v>
       </c>
       <c r="C81">
-        <v>-13.22468178832068</v>
+        <v>-13.62318494713088</v>
       </c>
       <c r="D81">
-        <v>9.424978211679321</v>
+        <v>9.340015052869122</v>
       </c>
       <c r="E81">
-        <v>24.11566</v>
+        <v>24.4292</v>
       </c>
       <c r="F81">
-        <v>24.76966</v>
+        <v>25.0832</v>
       </c>
       <c r="G81">
         <v>2.12</v>
@@ -7929,37 +7929,37 @@
         <v>2.07</v>
       </c>
       <c r="M81">
-        <v>5.840685828000001</v>
+        <v>5.914618560000001</v>
       </c>
       <c r="N81">
-        <v>-3.770685828</v>
+        <v>-3.844618560000001</v>
       </c>
       <c r="O81">
-        <v>-0.3770685828000001</v>
+        <v>-0.3844618560000001</v>
       </c>
       <c r="P81">
-        <v>-3.3936172452</v>
+        <v>-3.460156704000001</v>
       </c>
       <c r="Q81">
-        <v>-2.7636172452</v>
+        <v>-2.830156704000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3212510769877892</v>
+        <v>0.3350236308371787</v>
       </c>
       <c r="T81">
-        <v>4.261140557061048</v>
+        <v>4.474197584914101</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03544104341439678</v>
+        <v>0.03499803037171682</v>
       </c>
       <c r="W81">
-        <v>0.2274430019628852</v>
+        <v>0.2275474644383492</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3544104341439678</v>
+        <v>0.3499803037171682</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2490426977181151</v>
+        <v>0.2509426977181151</v>
       </c>
       <c r="C82">
-        <v>-13.62318494713088</v>
+        <v>-14.02016996022938</v>
       </c>
       <c r="D82">
-        <v>9.340015052869122</v>
+        <v>9.256570039770615</v>
       </c>
       <c r="E82">
-        <v>24.4292</v>
+        <v>24.74274</v>
       </c>
       <c r="F82">
-        <v>25.0832</v>
+        <v>25.39674</v>
       </c>
       <c r="G82">
         <v>2.12</v>
@@ -8011,37 +8011,37 @@
         <v>2.07</v>
       </c>
       <c r="M82">
-        <v>5.914618560000001</v>
+        <v>5.988551292</v>
       </c>
       <c r="N82">
-        <v>-3.844618560000001</v>
+        <v>-3.918551292</v>
       </c>
       <c r="O82">
-        <v>-0.3844618560000001</v>
+        <v>-0.3918551292</v>
       </c>
       <c r="P82">
-        <v>-3.460156704000001</v>
+        <v>-3.5266961628</v>
       </c>
       <c r="Q82">
-        <v>-2.830156704000001</v>
+        <v>-2.8966961628</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3350236308371787</v>
+        <v>0.3502459271970302</v>
       </c>
       <c r="T82">
-        <v>4.474197584914101</v>
+        <v>4.709681668330633</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03499803037171682</v>
+        <v>0.03456595592268329</v>
       </c>
       <c r="W82">
-        <v>0.2275474644383492</v>
+        <v>0.2276493475934313</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3499803037171682</v>
+        <v>0.3456595592268328</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2509426977181151</v>
+        <v>0.2528426977181151</v>
       </c>
       <c r="C83">
-        <v>-14.02016996022938</v>
+        <v>-14.41567715728957</v>
       </c>
       <c r="D83">
-        <v>9.256570039770615</v>
+        <v>9.174602842710431</v>
       </c>
       <c r="E83">
-        <v>24.74274</v>
+        <v>25.05628</v>
       </c>
       <c r="F83">
-        <v>25.39674</v>
+        <v>25.71028</v>
       </c>
       <c r="G83">
         <v>2.12</v>
@@ -8093,37 +8093,37 @@
         <v>2.07</v>
       </c>
       <c r="M83">
-        <v>5.988551292</v>
+        <v>6.062484024000001</v>
       </c>
       <c r="N83">
-        <v>-3.918551292</v>
+        <v>-3.992484024</v>
       </c>
       <c r="O83">
-        <v>-0.3918551292</v>
+        <v>-0.3992484024</v>
       </c>
       <c r="P83">
-        <v>-3.5266961628</v>
+        <v>-3.5932356216</v>
       </c>
       <c r="Q83">
-        <v>-2.8966961628</v>
+        <v>-2.9632356216</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3502459271970302</v>
+        <v>0.3671595898190874</v>
       </c>
       <c r="T83">
-        <v>4.709681668330633</v>
+        <v>4.971330649904557</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03456595592268329</v>
+        <v>0.03414441987484568</v>
       </c>
       <c r="W83">
-        <v>0.2276493475934313</v>
+        <v>0.2277487457935114</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3456595592268328</v>
+        <v>0.3414441987484568</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2528426977181151</v>
+        <v>0.2547426977181151</v>
       </c>
       <c r="C84">
-        <v>-14.41567715728957</v>
+        <v>-14.80974545204128</v>
       </c>
       <c r="D84">
-        <v>9.174602842710431</v>
+        <v>9.094074547958718</v>
       </c>
       <c r="E84">
-        <v>25.05628</v>
+        <v>25.36982</v>
       </c>
       <c r="F84">
-        <v>25.71028</v>
+        <v>26.02382</v>
       </c>
       <c r="G84">
         <v>2.12</v>
@@ -8175,37 +8175,37 @@
         <v>2.07</v>
       </c>
       <c r="M84">
-        <v>6.062484024000001</v>
+        <v>6.136416756</v>
       </c>
       <c r="N84">
-        <v>-3.992484024</v>
+        <v>-4.066416756</v>
       </c>
       <c r="O84">
-        <v>-0.3992484024</v>
+        <v>-0.4066416756</v>
       </c>
       <c r="P84">
-        <v>-3.5932356216</v>
+        <v>-3.6597750804</v>
       </c>
       <c r="Q84">
-        <v>-2.9632356216</v>
+        <v>-3.0297750804</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3671595898190874</v>
+        <v>0.3860630951025632</v>
       </c>
       <c r="T84">
-        <v>4.971330649904557</v>
+        <v>5.263761864604826</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03414441987484568</v>
+        <v>0.0337330413221367</v>
       </c>
       <c r="W84">
-        <v>0.2277487457935114</v>
+        <v>0.2278457488562402</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3414441987484568</v>
+        <v>0.337330413221367</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2547426977181151</v>
+        <v>0.2566426977181151</v>
       </c>
       <c r="C85">
-        <v>-14.80974545204128</v>
+        <v>-15.20241240387104</v>
       </c>
       <c r="D85">
-        <v>9.094074547958718</v>
+        <v>9.014947596128957</v>
       </c>
       <c r="E85">
-        <v>25.36982</v>
+        <v>25.68336</v>
       </c>
       <c r="F85">
-        <v>26.02382</v>
+        <v>26.33736</v>
       </c>
       <c r="G85">
         <v>2.12</v>
@@ -8257,37 +8257,37 @@
         <v>2.07</v>
       </c>
       <c r="M85">
-        <v>6.136416756</v>
+        <v>6.210349488</v>
       </c>
       <c r="N85">
-        <v>-4.066416756</v>
+        <v>-4.140349488</v>
       </c>
       <c r="O85">
-        <v>-0.4066416756</v>
+        <v>-0.4140349488</v>
       </c>
       <c r="P85">
-        <v>-3.6597750804</v>
+        <v>-3.7263145392</v>
       </c>
       <c r="Q85">
-        <v>-3.0297750804</v>
+        <v>-3.0963145392</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3860630951025632</v>
+        <v>0.4073295385464734</v>
       </c>
       <c r="T85">
-        <v>5.263761864604826</v>
+        <v>5.592746981142628</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0337330413221367</v>
+        <v>0.03333145749687316</v>
       </c>
       <c r="W85">
-        <v>0.2278457488562402</v>
+        <v>0.2279404423222373</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.337330413221367</v>
+        <v>0.3333145749687316</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.256642697718115</v>
+        <v>0.2585426977181151</v>
       </c>
       <c r="C86">
-        <v>-15.20241240387104</v>
+        <v>-15.59371427623405</v>
       </c>
       <c r="D86">
-        <v>9.014947596128959</v>
+        <v>8.93718572376595</v>
       </c>
       <c r="E86">
-        <v>25.68336</v>
+        <v>25.9969</v>
       </c>
       <c r="F86">
-        <v>26.33736</v>
+        <v>26.6509</v>
       </c>
       <c r="G86">
         <v>2.12</v>
@@ -8339,37 +8339,37 @@
         <v>2.07</v>
       </c>
       <c r="M86">
-        <v>6.210349487999999</v>
+        <v>6.284282220000001</v>
       </c>
       <c r="N86">
-        <v>-4.140349487999999</v>
+        <v>-4.21428222</v>
       </c>
       <c r="O86">
-        <v>-0.4140349487999999</v>
+        <v>-0.4214282220000001</v>
       </c>
       <c r="P86">
-        <v>-3.726314539199999</v>
+        <v>-3.792853998</v>
       </c>
       <c r="Q86">
-        <v>-3.096314539199999</v>
+        <v>-3.162853998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4073295385464732</v>
+        <v>0.4314315077829047</v>
       </c>
       <c r="T86">
-        <v>5.592746981142625</v>
+        <v>5.965596779885466</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03333145749687317</v>
+        <v>0.0329393227027923</v>
       </c>
       <c r="W86">
-        <v>0.2279404423222373</v>
+        <v>0.2280329077066816</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3333145749687317</v>
+        <v>0.3293932270279231</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2585426977181151</v>
+        <v>0.2604426977181151</v>
       </c>
       <c r="C87">
-        <v>-15.59371427623405</v>
+        <v>-15.98368609206895</v>
       </c>
       <c r="D87">
-        <v>8.93718572376595</v>
+        <v>8.860753907931052</v>
       </c>
       <c r="E87">
-        <v>25.9969</v>
+        <v>26.31044</v>
       </c>
       <c r="F87">
-        <v>26.6509</v>
+        <v>26.96444</v>
       </c>
       <c r="G87">
         <v>2.12</v>
@@ -8421,37 +8421,37 @@
         <v>2.07</v>
       </c>
       <c r="M87">
-        <v>6.284282220000001</v>
+        <v>6.358214952</v>
       </c>
       <c r="N87">
-        <v>-4.21428222</v>
+        <v>-4.288214952</v>
       </c>
       <c r="O87">
-        <v>-0.4214282220000001</v>
+        <v>-0.4288214952</v>
       </c>
       <c r="P87">
-        <v>-3.792853998</v>
+        <v>-3.859393456799999</v>
       </c>
       <c r="Q87">
-        <v>-3.162853998</v>
+        <v>-3.2293934568</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4314315077829047</v>
+        <v>0.4589766154816837</v>
       </c>
       <c r="T87">
-        <v>5.965596779885466</v>
+        <v>6.391710835591572</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0329393227027923</v>
+        <v>0.03255630732252728</v>
       </c>
       <c r="W87">
-        <v>0.2280329077066816</v>
+        <v>0.2281232227333481</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3293932270279231</v>
+        <v>0.3255630732252728</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2604426977181151</v>
+        <v>0.2623426977181151</v>
       </c>
       <c r="C88">
-        <v>-15.98368609206895</v>
+        <v>-16.37236168639319</v>
       </c>
       <c r="D88">
-        <v>8.860753907931052</v>
+        <v>8.785618313606813</v>
       </c>
       <c r="E88">
-        <v>26.31044</v>
+        <v>26.62398</v>
       </c>
       <c r="F88">
-        <v>26.96444</v>
+        <v>27.27798</v>
       </c>
       <c r="G88">
         <v>2.12</v>
@@ -8503,37 +8503,37 @@
         <v>2.07</v>
       </c>
       <c r="M88">
-        <v>6.358214952</v>
+        <v>6.432147684</v>
       </c>
       <c r="N88">
-        <v>-4.288214952</v>
+        <v>-4.362147684</v>
       </c>
       <c r="O88">
-        <v>-0.4288214952</v>
+        <v>-0.4362147684</v>
       </c>
       <c r="P88">
-        <v>-3.859393456799999</v>
+        <v>-3.9259329156</v>
       </c>
       <c r="Q88">
-        <v>-3.2293934568</v>
+        <v>-3.2959329156</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4589766154816837</v>
+        <v>0.4907594320571978</v>
       </c>
       <c r="T88">
-        <v>6.391710835591572</v>
+        <v>6.883380899867846</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03255630732252728</v>
+        <v>0.03218209689353271</v>
       </c>
       <c r="W88">
-        <v>0.2281232227333481</v>
+        <v>0.228211461552505</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3255630732252728</v>
+        <v>0.3218209689353271</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2623426977181151</v>
+        <v>0.264242697718115</v>
       </c>
       <c r="C89">
-        <v>-16.37236168639319</v>
+        <v>-16.75977375624501</v>
       </c>
       <c r="D89">
-        <v>8.785618313606813</v>
+        <v>8.711746243754988</v>
       </c>
       <c r="E89">
-        <v>26.62398</v>
+        <v>26.93752</v>
       </c>
       <c r="F89">
-        <v>27.27798</v>
+        <v>27.59152</v>
       </c>
       <c r="G89">
         <v>2.12</v>
@@ -8585,37 +8585,37 @@
         <v>2.07</v>
       </c>
       <c r="M89">
-        <v>6.432147684</v>
+        <v>6.506080416</v>
       </c>
       <c r="N89">
-        <v>-4.362147684</v>
+        <v>-4.436080415999999</v>
       </c>
       <c r="O89">
-        <v>-0.4362147684</v>
+        <v>-0.4436080415999999</v>
       </c>
       <c r="P89">
-        <v>-3.9259329156</v>
+        <v>-3.992472374399999</v>
       </c>
       <c r="Q89">
-        <v>-3.2959329156</v>
+        <v>-3.362472374399999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4907594320571978</v>
+        <v>0.5278393847286309</v>
       </c>
       <c r="T89">
-        <v>6.883380899867846</v>
+        <v>7.456995974856833</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03218209689353271</v>
+        <v>0.0318163912470153</v>
       </c>
       <c r="W89">
-        <v>0.228211461552505</v>
+        <v>0.2282976949439538</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3218209689353271</v>
+        <v>0.318163912470153</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.264242697718115</v>
+        <v>0.2661426977181151</v>
       </c>
       <c r="C90">
-        <v>-16.75977375624501</v>
+        <v>-17.14595390812684</v>
       </c>
       <c r="D90">
-        <v>8.711746243754988</v>
+        <v>8.639106091873158</v>
       </c>
       <c r="E90">
-        <v>26.93752</v>
+        <v>27.25106</v>
       </c>
       <c r="F90">
-        <v>27.59152</v>
+        <v>27.90506</v>
       </c>
       <c r="G90">
         <v>2.12</v>
@@ -8667,37 +8667,37 @@
         <v>2.07</v>
       </c>
       <c r="M90">
-        <v>6.506080416</v>
+        <v>6.580013148</v>
       </c>
       <c r="N90">
-        <v>-4.436080415999999</v>
+        <v>-4.510013148</v>
       </c>
       <c r="O90">
-        <v>-0.4436080415999999</v>
+        <v>-0.4510013148</v>
       </c>
       <c r="P90">
-        <v>-3.992472374399999</v>
+        <v>-4.0590118332</v>
       </c>
       <c r="Q90">
-        <v>-3.362472374399999</v>
+        <v>-3.4290118332</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5278393847286309</v>
+        <v>0.5716611469766884</v>
       </c>
       <c r="T90">
-        <v>7.456995974856833</v>
+        <v>8.134904699843819</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.0318163912470153</v>
+        <v>0.031458903704914</v>
       </c>
       <c r="W90">
-        <v>0.2282976949439538</v>
+        <v>0.2283819905063813</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.318163912470153</v>
+        <v>0.31458903704914</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2661426977181151</v>
+        <v>0.2680426977181151</v>
       </c>
       <c r="C91">
-        <v>-17.14595390812684</v>
+        <v>-17.53093270309476</v>
       </c>
       <c r="D91">
-        <v>8.639106091873158</v>
+        <v>8.567667296905237</v>
       </c>
       <c r="E91">
-        <v>27.25106</v>
+        <v>27.5646</v>
       </c>
       <c r="F91">
-        <v>27.90506</v>
+        <v>28.2186</v>
       </c>
       <c r="G91">
         <v>2.12</v>
@@ -8749,37 +8749,37 @@
         <v>2.07</v>
       </c>
       <c r="M91">
-        <v>6.580013148</v>
+        <v>6.65394588</v>
       </c>
       <c r="N91">
-        <v>-4.510013148</v>
+        <v>-4.58394588</v>
       </c>
       <c r="O91">
-        <v>-0.4510013148</v>
+        <v>-0.458394588</v>
       </c>
       <c r="P91">
-        <v>-4.0590118332</v>
+        <v>-4.125551292</v>
       </c>
       <c r="Q91">
-        <v>-3.4290118332</v>
+        <v>-3.495551292</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5716611469766884</v>
+        <v>0.6242472616743573</v>
       </c>
       <c r="T91">
-        <v>8.134904699843819</v>
+        <v>8.948395169828203</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.031458903704914</v>
+        <v>0.03110936033041495</v>
       </c>
       <c r="W91">
-        <v>0.2283819905063813</v>
+        <v>0.2284644128340882</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.31458903704914</v>
+        <v>0.3110936033041496</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2680426977181151</v>
+        <v>0.2699426977181151</v>
       </c>
       <c r="C92">
-        <v>-17.53093270309476</v>
+        <v>-17.91473969962923</v>
       </c>
       <c r="D92">
-        <v>8.567667296905237</v>
+        <v>8.497400300370769</v>
       </c>
       <c r="E92">
-        <v>27.5646</v>
+        <v>27.87814</v>
       </c>
       <c r="F92">
-        <v>28.2186</v>
+        <v>28.53214</v>
       </c>
       <c r="G92">
         <v>2.12</v>
@@ -8831,37 +8831,37 @@
         <v>2.07</v>
       </c>
       <c r="M92">
-        <v>6.65394588</v>
+        <v>6.727878612</v>
       </c>
       <c r="N92">
-        <v>-4.58394588</v>
+        <v>-4.657878612</v>
       </c>
       <c r="O92">
-        <v>-0.458394588</v>
+        <v>-0.4657878612</v>
       </c>
       <c r="P92">
-        <v>-4.125551292</v>
+        <v>-4.1920907508</v>
       </c>
       <c r="Q92">
-        <v>-3.495551292</v>
+        <v>-3.5620907508</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6242472616743573</v>
+        <v>0.6885191796381748</v>
       </c>
       <c r="T92">
-        <v>8.948395169828203</v>
+        <v>9.942661299809114</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03110936033041495</v>
+        <v>0.03076749922788292</v>
       </c>
       <c r="W92">
-        <v>0.2284644128340882</v>
+        <v>0.2285450236820652</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3110936033041496</v>
+        <v>0.3076749922788292</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2699426977181151</v>
+        <v>0.271842697718115</v>
       </c>
       <c r="C93">
-        <v>-17.91473969962923</v>
+        <v>-18.29740349441331</v>
       </c>
       <c r="D93">
-        <v>8.497400300370769</v>
+        <v>8.428276505586688</v>
       </c>
       <c r="E93">
-        <v>27.87814</v>
+        <v>28.19168</v>
       </c>
       <c r="F93">
-        <v>28.53214</v>
+        <v>28.84568</v>
       </c>
       <c r="G93">
         <v>2.12</v>
@@ -8913,37 +8913,37 @@
         <v>2.07</v>
       </c>
       <c r="M93">
-        <v>6.727878612</v>
+        <v>6.801811344000001</v>
       </c>
       <c r="N93">
-        <v>-4.657878612</v>
+        <v>-4.731811344</v>
       </c>
       <c r="O93">
-        <v>-0.4657878612</v>
+        <v>-0.4731811344000001</v>
       </c>
       <c r="P93">
-        <v>-4.1920907508</v>
+        <v>-4.258630209600001</v>
       </c>
       <c r="Q93">
-        <v>-3.5620907508</v>
+        <v>-3.628630209600001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6885191796381748</v>
+        <v>0.7688590770929468</v>
       </c>
       <c r="T93">
-        <v>9.942661299809114</v>
+        <v>11.18549396228526</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03076749922788292</v>
+        <v>0.03043306988844941</v>
       </c>
       <c r="W93">
-        <v>0.2285450236820652</v>
+        <v>0.2286238821203036</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3076749922788292</v>
+        <v>0.304330698884494</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.271842697718115</v>
+        <v>0.2737426977181151</v>
       </c>
       <c r="C94">
-        <v>-18.29740349441331</v>
+        <v>-18.67895176113672</v>
       </c>
       <c r="D94">
-        <v>8.428276505586688</v>
+        <v>8.360268238863286</v>
       </c>
       <c r="E94">
-        <v>28.19168</v>
+        <v>28.50522</v>
       </c>
       <c r="F94">
-        <v>28.84568</v>
+        <v>29.15922</v>
       </c>
       <c r="G94">
         <v>2.12</v>
@@ -8995,37 +8995,37 @@
         <v>2.07</v>
       </c>
       <c r="M94">
-        <v>6.801811344000001</v>
+        <v>6.875744076</v>
       </c>
       <c r="N94">
-        <v>-4.731811344</v>
+        <v>-4.805744076</v>
       </c>
       <c r="O94">
-        <v>-0.4731811344000001</v>
+        <v>-0.4805744076</v>
       </c>
       <c r="P94">
-        <v>-4.258630209600001</v>
+        <v>-4.3251696684</v>
       </c>
       <c r="Q94">
-        <v>-3.628630209600001</v>
+        <v>-3.6951696684</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7688590770929468</v>
+        <v>0.8721532309633678</v>
       </c>
       <c r="T94">
-        <v>11.18549396228526</v>
+        <v>12.78342167118315</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03043306988844941</v>
+        <v>0.03010583257782093</v>
       </c>
       <c r="W94">
-        <v>0.2286238821203036</v>
+        <v>0.2287010446781498</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.304330698884494</v>
+        <v>0.3010583257782092</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2737426977181151</v>
+        <v>0.2756426977181151</v>
       </c>
       <c r="C95">
-        <v>-18.67895176113672</v>
+        <v>-19.05941128743611</v>
       </c>
       <c r="D95">
-        <v>8.360268238863286</v>
+        <v>8.293348712563892</v>
       </c>
       <c r="E95">
-        <v>28.50522</v>
+        <v>28.81876</v>
       </c>
       <c r="F95">
-        <v>29.15922</v>
+        <v>29.47276</v>
       </c>
       <c r="G95">
         <v>2.12</v>
@@ -9077,37 +9077,37 @@
         <v>2.07</v>
       </c>
       <c r="M95">
-        <v>6.875744076</v>
+        <v>6.949676808</v>
       </c>
       <c r="N95">
-        <v>-4.805744076</v>
+        <v>-4.879676808</v>
       </c>
       <c r="O95">
-        <v>-0.4805744076</v>
+        <v>-0.4879676808</v>
       </c>
       <c r="P95">
-        <v>-4.3251696684</v>
+        <v>-4.3917091272</v>
       </c>
       <c r="Q95">
-        <v>-3.6951696684</v>
+        <v>-3.761709127200001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8721532309633678</v>
+        <v>1.009878769457263</v>
       </c>
       <c r="T95">
-        <v>12.78342167118315</v>
+        <v>14.91399194971368</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03010583257782093</v>
+        <v>0.02978555776316325</v>
       </c>
       <c r="W95">
-        <v>0.2287010446781498</v>
+        <v>0.2287765654794461</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3010583257782092</v>
+        <v>0.2978555776316325</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2756426977181151</v>
+        <v>0.2775426977181151</v>
       </c>
       <c r="C96">
-        <v>-19.05941128743611</v>
+        <v>-19.43880801007551</v>
       </c>
       <c r="D96">
-        <v>8.293348712563892</v>
+        <v>8.22749198992449</v>
       </c>
       <c r="E96">
-        <v>28.81876</v>
+        <v>29.1323</v>
       </c>
       <c r="F96">
-        <v>29.47276</v>
+        <v>29.7863</v>
       </c>
       <c r="G96">
         <v>2.12</v>
@@ -9159,37 +9159,37 @@
         <v>2.07</v>
       </c>
       <c r="M96">
-        <v>6.949676808</v>
+        <v>7.023609540000001</v>
       </c>
       <c r="N96">
-        <v>-4.879676808</v>
+        <v>-4.95360954</v>
       </c>
       <c r="O96">
-        <v>-0.4879676808</v>
+        <v>-0.4953609540000001</v>
       </c>
       <c r="P96">
-        <v>-4.3917091272</v>
+        <v>-4.458248586000001</v>
       </c>
       <c r="Q96">
-        <v>-3.761709127200001</v>
+        <v>-3.828248586000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.009878769457263</v>
+        <v>1.202694523348716</v>
       </c>
       <c r="T96">
-        <v>14.91399194971368</v>
+        <v>17.89679033965643</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02978555776316325</v>
+        <v>0.02947202557618259</v>
       </c>
       <c r="W96">
-        <v>0.2287765654794461</v>
+        <v>0.2288504963691362</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2978555776316325</v>
+        <v>0.2947202557618258</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2775426977181151</v>
+        <v>0.2794426977181151</v>
       </c>
       <c r="C97">
-        <v>-19.43880801007551</v>
+        <v>-19.8171670484636</v>
       </c>
       <c r="D97">
-        <v>8.22749198992449</v>
+        <v>8.162672951536402</v>
       </c>
       <c r="E97">
-        <v>29.1323</v>
+        <v>29.44584</v>
       </c>
       <c r="F97">
-        <v>29.7863</v>
+        <v>30.09984</v>
       </c>
       <c r="G97">
         <v>2.12</v>
@@ -9241,37 +9241,37 @@
         <v>2.07</v>
       </c>
       <c r="M97">
-        <v>7.023609540000001</v>
+        <v>7.097542272</v>
       </c>
       <c r="N97">
-        <v>-4.95360954</v>
+        <v>-5.027542272</v>
       </c>
       <c r="O97">
-        <v>-0.4953609540000001</v>
+        <v>-0.5027542272</v>
       </c>
       <c r="P97">
-        <v>-4.458248586000001</v>
+        <v>-4.5247880448</v>
       </c>
       <c r="Q97">
-        <v>-3.828248586000001</v>
+        <v>-3.8947880448</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.202694523348716</v>
+        <v>1.491918154185896</v>
       </c>
       <c r="T97">
-        <v>17.89679033965643</v>
+        <v>22.37098792457054</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02947202557618259</v>
+        <v>0.02916502530976402</v>
       </c>
       <c r="W97">
-        <v>0.2288504963691362</v>
+        <v>0.2289228870319577</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2947202557618258</v>
+        <v>0.2916502530976401</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.279442697718115</v>
+        <v>0.281342697718115</v>
       </c>
       <c r="C98">
-        <v>-19.81716704846359</v>
+        <v>-20.19451273659909</v>
       </c>
       <c r="D98">
-        <v>8.162672951536404</v>
+        <v>8.098867263400908</v>
       </c>
       <c r="E98">
-        <v>29.44584</v>
+        <v>29.75938</v>
       </c>
       <c r="F98">
-        <v>30.09984</v>
+        <v>30.41338</v>
       </c>
       <c r="G98">
         <v>2.12</v>
@@ -9323,37 +9323,37 @@
         <v>2.07</v>
       </c>
       <c r="M98">
-        <v>7.097542271999999</v>
+        <v>7.171475004</v>
       </c>
       <c r="N98">
-        <v>-5.027542271999999</v>
+        <v>-5.101475004</v>
       </c>
       <c r="O98">
-        <v>-0.5027542272</v>
+        <v>-0.5101475004</v>
       </c>
       <c r="P98">
-        <v>-4.524788044799999</v>
+        <v>-4.591327503600001</v>
       </c>
       <c r="Q98">
-        <v>-3.894788044799999</v>
+        <v>-3.961327503600001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.491918154185892</v>
+        <v>1.973957538914523</v>
       </c>
       <c r="T98">
-        <v>22.37098792457048</v>
+        <v>29.82798389942731</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02916502530976403</v>
+        <v>0.02886435494574584</v>
       </c>
       <c r="W98">
-        <v>0.2289228870319577</v>
+        <v>0.2289937851037931</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2916502530976403</v>
+        <v>0.2886435494574583</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.281342697718115</v>
+        <v>0.2832426977181151</v>
       </c>
       <c r="C99">
-        <v>-20.19451273659909</v>
+        <v>-20.57086865352949</v>
       </c>
       <c r="D99">
-        <v>8.098867263400908</v>
+        <v>8.036051346470506</v>
       </c>
       <c r="E99">
-        <v>29.75938</v>
+        <v>30.07292</v>
       </c>
       <c r="F99">
-        <v>30.41338</v>
+        <v>30.72692</v>
       </c>
       <c r="G99">
         <v>2.12</v>
@@ -9405,37 +9405,37 @@
         <v>2.07</v>
       </c>
       <c r="M99">
-        <v>7.171475004</v>
+        <v>7.245407736000001</v>
       </c>
       <c r="N99">
-        <v>-5.101475004</v>
+        <v>-5.175407736</v>
       </c>
       <c r="O99">
-        <v>-0.5101475004</v>
+        <v>-0.5175407736000001</v>
       </c>
       <c r="P99">
-        <v>-4.591327503600001</v>
+        <v>-4.6578669624</v>
       </c>
       <c r="Q99">
-        <v>-3.961327503600001</v>
+        <v>-4.0278669624</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.973957538914523</v>
+        <v>2.938036308371784</v>
       </c>
       <c r="T99">
-        <v>29.82798389942731</v>
+        <v>44.74197584914096</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02886435494574584</v>
+        <v>0.02856982071160557</v>
       </c>
       <c r="W99">
-        <v>0.2289937851037931</v>
+        <v>0.2290632362762034</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2886435494574583</v>
+        <v>0.2856982071160556</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2832426977181151</v>
+        <v>0.2851426977181151</v>
       </c>
       <c r="C100">
-        <v>-20.57086865352949</v>
+        <v>-20.94625765240325</v>
       </c>
       <c r="D100">
-        <v>8.036051346470506</v>
+        <v>7.974202347596747</v>
       </c>
       <c r="E100">
-        <v>30.07292</v>
+        <v>30.38646</v>
       </c>
       <c r="F100">
-        <v>30.72692</v>
+        <v>31.04046</v>
       </c>
       <c r="G100">
         <v>2.12</v>
@@ -9487,37 +9487,37 @@
         <v>2.07</v>
       </c>
       <c r="M100">
-        <v>7.245407736000001</v>
+        <v>7.319340468</v>
       </c>
       <c r="N100">
-        <v>-5.175407736</v>
+        <v>-5.249340468</v>
       </c>
       <c r="O100">
-        <v>-0.5175407736000001</v>
+        <v>-0.5249340468</v>
       </c>
       <c r="P100">
-        <v>-4.6578669624</v>
+        <v>-4.724406421199999</v>
       </c>
       <c r="Q100">
-        <v>-4.0278669624</v>
+        <v>-4.0944064212</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.938036308371784</v>
+        <v>5.830272616743567</v>
       </c>
       <c r="T100">
-        <v>44.74197584914096</v>
+        <v>89.48395169828193</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02856982071160557</v>
+        <v>0.0282812366640136</v>
       </c>
       <c r="W100">
-        <v>0.2290632362762034</v>
+        <v>0.2291312843946256</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2856982071160556</v>
+        <v>0.282812366640136</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2851426977181151</v>
-      </c>
-      <c r="C101">
-        <v>-20.94625765240325</v>
-      </c>
-      <c r="D101">
-        <v>7.974202347596747</v>
-      </c>
-      <c r="E101">
-        <v>30.38646</v>
-      </c>
-      <c r="F101">
-        <v>31.04046</v>
-      </c>
-      <c r="G101">
-        <v>2.12</v>
-      </c>
-      <c r="H101">
-        <v>30.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.7</v>
-      </c>
-      <c r="K101">
-        <v>0.63</v>
-      </c>
-      <c r="L101">
-        <v>2.07</v>
-      </c>
-      <c r="M101">
-        <v>7.319340468</v>
-      </c>
-      <c r="N101">
-        <v>-5.249340468</v>
-      </c>
-      <c r="O101">
-        <v>-0.5249340468</v>
-      </c>
-      <c r="P101">
-        <v>-4.724406421199999</v>
-      </c>
-      <c r="Q101">
-        <v>-4.0944064212</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.830272616743567</v>
-      </c>
-      <c r="T101">
-        <v>89.48395169828193</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0282812366640136</v>
-      </c>
-      <c r="W101">
-        <v>0.2291312843946256</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.282812366640136</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
